--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,414 +656,426 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45197</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45106</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45015</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44833</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44378</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44287</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44105</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44014</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43923</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43734</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43643</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43552</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43370</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43279</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43188</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43006</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42915</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42824</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1812900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1438900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1364700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1431400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1320100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1276900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1257900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1174700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1070100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>980000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1002100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>876600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>806300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>644600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1077300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1959300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1919900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2016100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1967800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1835300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1813700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1836900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1521500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1492500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1395500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1432200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1369800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1193700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1277500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1130400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1056500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1033600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1012000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>956700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>904600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>914300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>905800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1087100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1757300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1647600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1723200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1658300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1534600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1543100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1547200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-53600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-30800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-49700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>83200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-19600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>44300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-53600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-9900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-55900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-28000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-261200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-9800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>202000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>272300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>292900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>309500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>300700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>270600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>289700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>225100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>290400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>261600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>273100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>236800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1096,100 +1108,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E12" s="3">
         <v>10100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1280,8 +1296,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1289,71 +1308,71 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>9700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>8800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>40200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>25600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>68500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-11000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-8400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
@@ -1361,19 +1380,22 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>9100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>12100</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1407,11 +1429,11 @@
       <c r="M15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="3">
         <v>2300</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>10</v>
@@ -1428,8 +1450,8 @@
       <c r="T15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1464,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1495,192 +1520,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1597900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1572600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1485100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1526500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1458900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1272400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1362600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1216900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1149100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1136600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1099800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1030000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>982700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>983200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1011600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1244800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1863600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1713800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1776600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1734800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1591700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1591200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1619300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-133700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-120400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-95100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-138800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-104700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-42200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-79000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-156600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-97700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-129200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-106100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-176900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-367000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-167500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>95700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>206100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>239500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>233000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>243600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>222500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>217600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>159500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>226900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>202300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>204400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>160900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1713,468 +1745,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>7300</v>
+        <v>-20400</v>
       </c>
       <c r="E20" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-9900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-117400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-44300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-42100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>34600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>37700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>94800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-49000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>10500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>10700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-47200</v>
+        <v>273300</v>
       </c>
       <c r="E21" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-52500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-132600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-99200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>80700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-38700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-119800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-305300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-149200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>166500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>260100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>297600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>282500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>296700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>287800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>262300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>220400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>284600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>267000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>267600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>221800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>75100</v>
+        <v>97600</v>
       </c>
       <c r="E22" s="3">
+        <v>77500</v>
+      </c>
+      <c r="F22" s="3">
         <v>73600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>72400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>73300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>56800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>55100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>58900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>64900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>58800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>59100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>48600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>32200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-201500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-203900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-284900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-256400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-94400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-125200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-63400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-136000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-120600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-125700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-172900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-175300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-239900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-422000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-248700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>76000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>173000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>210900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>203200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>217700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>205700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>180500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>152300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>217900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>202900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>205600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>152500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-13200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>32900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-11000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-16600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>119800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-85200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-167600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-87200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>41700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>36900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>35300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>66400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>55900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>64000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>44300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2265,192 +2313,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>75600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-203900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-206900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-280600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-243200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-127300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-121700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-119400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-112700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-134700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-171200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-295100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-154700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-254400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-161500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>67500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>131300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>168000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>163100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>172200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>168800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>145200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>124800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>151500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>147000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>141600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>108200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-204100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-206300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-281200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-243100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-127600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-122200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-52800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-120300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-113600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-135300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-171600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-295900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-155500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-255900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-162900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>66900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>131300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>167900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>163000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>172500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>168700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>145100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>125300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>151500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>147100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>141600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>108200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2541,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2573,8 +2633,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>10</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>10</v>
@@ -2591,11 +2651,11 @@
       <c r="R29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T29" s="3">
         <v>400</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>10</v>
@@ -2603,11 +2663,11 @@
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X29" s="3">
         <v>5400</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
@@ -2615,11 +2675,11 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -2633,8 +2693,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2725,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2817,192 +2883,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-7300</v>
+        <v>20400</v>
       </c>
       <c r="E32" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="F32" s="3">
         <v>9900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>117400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>44300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>42100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-34600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-37700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-94800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>49000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-204100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-206300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-281200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-243100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-127600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-122200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-52800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-120300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-113600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-135300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-171600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-295900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-155500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-255900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-162900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>67300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>131300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>167900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>163000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>177900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>168700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>145100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>125300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>122800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>147100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>141600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>108200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3093,197 +3168,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-204100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-206300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-281200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-243100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-127600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-122200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-52800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-120300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-113600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-135300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-171600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-295900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-155500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-255900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-162900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>67300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>131300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>167900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>163000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>177900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>168700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>145100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>125300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>122800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>147100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>141600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>108200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45197</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45106</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45015</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44833</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44378</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44287</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44105</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44014</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43923</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43734</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43643</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43552</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43370</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43279</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43188</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43006</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42915</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42824</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3316,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3350,100 +3435,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>823500</v>
+      </c>
+      <c r="E41" s="3">
         <v>374100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>525700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>567800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>658600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>670500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>770200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1151800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1478600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1430600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1269300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1359300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1873300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1441300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1947100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1833600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2350500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1477300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1301400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1228400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>773600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>683400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>593000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>437900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>423300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>726600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>696900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>672200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>697700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3534,610 +3623,631 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1108400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1206300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1080300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1113700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>990500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1073800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1064000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1029000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>904800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>938600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>875000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>887700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>852800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>722400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>627600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>889500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1074700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1287600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1209400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1175800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1014500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1198300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1181000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>722200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>851700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>824300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>818600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>660500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1767300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1690000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1636300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1549100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1470700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1392400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1345800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1387800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1382600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1325700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1305400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1395800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1422300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1183300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1225900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1168700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1118800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1015200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>970700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>991600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1012600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>931000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>900800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>929500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E45" s="3">
         <v>50800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>49000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>41400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>121400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>342200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>344800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>336600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>260900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>99600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>99000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>62400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>48600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>35700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>151200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>55700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>70500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>110900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>34300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>36900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3751800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3321200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3291300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3287500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3158300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3170300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3211600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3610000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3806000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3816300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3791900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3987600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4485000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3607900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3900200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4026100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4643000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3838700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3543900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3427400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2849300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2848400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2826000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E47" s="3">
         <v>21800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1700</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>5900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>10700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>25300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>54100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>53500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>55100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>4700</v>
       </c>
       <c r="AB47" s="3">
         <v>4700</v>
       </c>
       <c r="AC47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>4400</v>
       </c>
       <c r="AE47" s="3">
         <v>4400</v>
       </c>
       <c r="AF47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AG47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2176300</v>
+      </c>
+      <c r="E48" s="3">
         <v>2177600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2215300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2253600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2300200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2302200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2343200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2411500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2470800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2494100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2530300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2527000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2574400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2191800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2226600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2300700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2320600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2249500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2212200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2235000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2167600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2123000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2102600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>827400</v>
+      </c>
+      <c r="E49" s="3">
         <v>831100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>835000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>838800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>841900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>824600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>828400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>832200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>836000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>839800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>833900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>790900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>780500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>107900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>108400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>109100</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3600</v>
       </c>
       <c r="T49" s="3">
         <v>3600</v>
@@ -4146,25 +4256,25 @@
         <v>3600</v>
       </c>
       <c r="V49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W49" s="3">
         <v>3700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>4300</v>
       </c>
       <c r="AA49" s="3">
         <v>4300</v>
       </c>
       <c r="AB49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AC49" s="3">
         <v>4400</v>
@@ -4173,13 +4283,16 @@
         <v>4400</v>
       </c>
       <c r="AE49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AF49" s="3">
         <v>4500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4270,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4362,100 +4478,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>193400</v>
+      </c>
+      <c r="E52" s="3">
         <v>186400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>186100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>183700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>363500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>409900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>603100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>632300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>623700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>588900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>585000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>556400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>536500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>692700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>803200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>554800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>624700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>600100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>574700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>606300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>611100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>653300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>624100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>601300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>502400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>497400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>504400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>476000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>494300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4546,100 +4668,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6950100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6538100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6545200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6574700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6666200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6713600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6989300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7490600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7737300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7740800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7741100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7867800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8383900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6604400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7043300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7001100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7606000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6701600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6345100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6297700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5685900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5682100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5611800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4672,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4706,560 +4835,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1106800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1030300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>974400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>948200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>919800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>848000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>810700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>762900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>720300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>644800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>607100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>540800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>558900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>483100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>512000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>740700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1058300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1140500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1116400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1072800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>902600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>882400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>837500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>819600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>693100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>762100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>726000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>691600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>579700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E58" s="3">
         <v>64200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>55100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>355400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>347700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>49100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>47800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>47900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>40200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>340700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>335500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>352800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>52700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>50200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>37600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>33300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>32400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>31400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>25000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>128100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>31200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1026700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1255500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1155400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1092200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>979000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1034100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1021500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1012900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1106200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1157900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>876400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>907000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>809800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>677700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>575900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>640700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>652200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>687600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>660400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>651100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>648100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>904800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>888500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>851100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>896800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>883200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>937800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2198300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2350000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2185800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2095500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1952500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2237500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2179900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1824900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1876000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1850500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1531400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1488000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1709400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1496300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1440700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1434100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1760700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1865700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1810100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1756300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1582100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1812200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1854100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4018700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3811000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3814900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3815800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3814900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3428000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3424800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3734000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3742700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3546700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3552700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3525200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3532900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2659000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3050600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2978200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2984100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2132200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2113300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2214900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1864000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1869700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1858400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1229000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1232800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1173400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1108000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1142600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1093700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1158700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1549500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1669800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1918800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2096700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2161600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2284600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1277100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1282500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1132400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1099300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1086700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>953000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1005400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1001700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>883800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>944600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>982800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>725400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>780900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>752400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>818800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>872200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5350,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5442,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5534,100 +5688,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7449800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7397500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7177600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7022900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6913700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6759700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6763900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7108900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7289000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7316500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7181300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7175300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7527400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5432900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5774300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5545200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5844600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5085100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4876900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4977100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4448300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4566200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4657600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5660,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5752,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5844,8 +6008,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5936,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6028,100 +6198,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E72" s="3">
         <v>540900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>745000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>951300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1232500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1475700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1604200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1727500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1781400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1902800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2017400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2153700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2326400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2623500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2780000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3036900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3201300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3146200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3027300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2871900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2713200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2548700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2392500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6212,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6304,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6396,100 +6578,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-499700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-859400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-632400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-448200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-247500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-46100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>225400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>381700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>448300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>424300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>559800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>692500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>856500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1171500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1269000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1455900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1761400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1616500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1468200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1320600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1237600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1115900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>954200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6580,197 +6768,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45197</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45106</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45015</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44833</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44378</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44287</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44105</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44014</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43923</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43734</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43643</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43552</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43370</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43279</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43188</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43006</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42915</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42824</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-204100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-206300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-281200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-243100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-127600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-122200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-52800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-120300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-113600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-135300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-171600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-295900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-155500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-255900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-162900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>67300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>131300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>167900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>163000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>177900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>168700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>145100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>125300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>122800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>147100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>141600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>108200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6803,100 +7000,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E83" s="3">
         <v>79200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>83900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>84200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>83800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>85200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>85700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>81600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>68100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>60500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>57900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>55100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>53700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>53000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>59500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6987,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7079,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7171,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7263,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7355,100 +7568,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-110500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-182800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-46200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-35700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-61500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-270200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-76500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>211000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-170200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-132100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-228400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-331300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>204100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>246900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>229500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>242200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>202500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>170200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>230600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>166600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>290600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>222300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>111700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>142500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7481,100 +7700,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-37500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-48500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-113400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-40900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-37100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7665,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7757,100 +7983,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-66700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-45800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-318600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-19100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-147300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-121200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-40900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-40700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-99700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-59000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7883,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7898,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>-1000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="J96" s="3">
         <v>-1100</v>
@@ -7913,16 +8146,16 @@
         <v>-1100</v>
       </c>
       <c r="L96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-1100</v>
       </c>
       <c r="N96" s="3">
         <v>-1100</v>
       </c>
       <c r="O96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="P96" s="3">
         <v>-1000</v>
@@ -7931,52 +8164,55 @@
         <v>-1000</v>
       </c>
       <c r="R96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-12400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-12600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-12700</v>
       </c>
       <c r="V96" s="3">
         <v>-12700</v>
       </c>
       <c r="W96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="X96" s="3">
         <v>-12600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AD96" s="3">
         <v>-12000</v>
       </c>
       <c r="AE96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8067,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8159,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8251,280 +8493,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>397500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>165200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>73500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-293700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>182300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-316400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>875100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-439100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>365500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-32000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>770900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-118100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>249700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-118100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>82900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>19400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>449400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-151500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-88300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-99700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-381700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-326800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>48000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>161300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-90000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-514000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>431000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-504800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>116500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-516800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>873200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>175900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>73100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>450900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>90200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>252600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>28600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>23600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>27300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,426 +656,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45197</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45106</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45015</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44833</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44378</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44287</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44105</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44014</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43923</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43734</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43643</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43552</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43370</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43279</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43188</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43006</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42915</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42824</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1702800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1812900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1438900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1364700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1431400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1320100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1276900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1257900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1174700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1070100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>980000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1002100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>876600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>806300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>644600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1077300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1959300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1919900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2016100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1967800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1835300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1813700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2138300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1521500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1492500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1395500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1432200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1369800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1193700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1277500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1130400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1056500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1033600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1012000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>956700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>904600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>914300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>905800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1087100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1757300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1647600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1723200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1658300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1534600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1543100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-435500</v>
+      </c>
+      <c r="E10" s="3">
         <v>291400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-53600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-30800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-49700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>83200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-19600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>44300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-53600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-9900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-55900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-108000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-261200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-9800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>202000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>272300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>292900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>309500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>300700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>270600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>289700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>225100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>290400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>261600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>273100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>236800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1109,103 +1122,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E12" s="3">
         <v>11500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>18500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1299,8 +1316,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1311,71 +1331,71 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>9700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>40200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>25600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>68500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-11000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1383,19 +1403,22 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>9100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>10800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>12100</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1432,11 +1455,11 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3">
         <v>2300</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>10</v>
@@ -1453,8 +1476,8 @@
       <c r="U15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1547,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2230400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1597900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1572600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1485100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1526500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1458900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1272400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1362600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1216900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1149100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1136600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1099800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1030000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>982700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>983200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1011600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1244800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1863600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1713800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1776600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1734800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1591700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1591200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-527600</v>
+      </c>
+      <c r="E18" s="3">
         <v>215000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-133700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-120400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-95100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-138800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-104700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-42200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-79000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-156600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-97700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-129200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-106100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-176900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-367000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-167500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>95700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>206100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>239500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>233000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>243600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>222500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>217600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>159500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>226900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>202300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>204400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>160900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,483 +1779,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-20400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-117400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-44300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-42100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>34600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>37700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>94800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>31100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-49000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-9500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>11000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>10500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-447400</v>
+      </c>
+      <c r="E21" s="3">
         <v>273300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-44800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-52500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-132600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-99200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>80700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-32800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-119800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-305300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-149200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>166500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>260100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>297600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>282500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>296700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>287800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>262300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>220400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>284600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>267000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>267600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>221800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E22" s="3">
         <v>97600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>77500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>73600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>73300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>56800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>55100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>58900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>64900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>58800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>59100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>59800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>61500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>53000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>48600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>25800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-605500</v>
+      </c>
+      <c r="E23" s="3">
         <v>97000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-201500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-203900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-284900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-256400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-94400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-125200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-136000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-120600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-125700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-172900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-175300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-239900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-422000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-248700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>173000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>210900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>203200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>217700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>205700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>180500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>152300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>217900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>202900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>205600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>152500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>21400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-13200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>32900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-16600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>119800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-85200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-167600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-87200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>42900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>40100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>45500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>35300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>66400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>55900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>64000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>44300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2365,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-616500</v>
+      </c>
+      <c r="E26" s="3">
         <v>75600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-203900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-206900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-280600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-243200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-127300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-121700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-119400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-112700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-134700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-171200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-295100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-154700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-254400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-161500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>67500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>131300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>168000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>163100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>172200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>168800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>145200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>124800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>151500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>147000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>141600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>108200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-616700</v>
+      </c>
+      <c r="E27" s="3">
         <v>75400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-204100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-206300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-281200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-243100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-127600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-122200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-52800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-120300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-113600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-135300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-171600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-155500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-255900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-162900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>66900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>131300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>167900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>163000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>172500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>168700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>145100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>125300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>151500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>147100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>141600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>108200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2636,8 +2697,8 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>10</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>10</v>
@@ -2654,11 +2715,11 @@
       <c r="S29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U29" s="3">
         <v>400</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
@@ -2666,11 +2727,11 @@
       <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y29" s="3">
         <v>5400</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -2678,11 +2739,11 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -2696,8 +2757,11 @@
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,198 +2953,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>20400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>117400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>44300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>42100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-34600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-37700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-94800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-31100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>49000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>9500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-616700</v>
+      </c>
+      <c r="E33" s="3">
         <v>75400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-204100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-206300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-281200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-243100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-127600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-122200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-52800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-120300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-113600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-135300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-171600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-155500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-255900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-162900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>67300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>131300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>167900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>163000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>177900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>168700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>145100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>125300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>122800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>147100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>141600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>108200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3247,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-616700</v>
+      </c>
+      <c r="E35" s="3">
         <v>75400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-204100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-206300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-281200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-243100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-127600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-122200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-52800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-120300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-113600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-135300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-171600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-155500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-255900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-162900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>67300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>131300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>167900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>163000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>177900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>168700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>145100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>125300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>122800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>147100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>141600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>108200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45197</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45106</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45015</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44833</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44378</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44287</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44105</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44014</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43923</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43734</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43643</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43552</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43370</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43279</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43188</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43006</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42915</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42824</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,103 +3522,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E41" s="3">
         <v>823500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>374100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>525700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>567800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>658600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>670500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>770200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1151800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1478600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1430600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1269300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1359300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1873300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1441300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1947100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1833600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2350500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1477300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1301400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1228400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>773600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>683400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>593000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>437900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>423300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>726600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>696900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>672200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>697700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3626,631 +3716,652 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1404300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1108400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1206300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1080300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1113700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>990500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1073800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1064000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1029000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>904800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>938600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>875000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>887700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>852800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>722400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>627600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>889500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1074700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1287600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1209400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1175800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1014500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1198300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>722200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>851700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>824300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>818600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>660500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1797500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1767300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1690000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1636300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1549100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1470700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1392400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1345800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1387800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1382600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1325700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1305400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1395800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1422300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1183300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1225900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1168700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1118800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1015200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>970700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>991600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1012600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>931000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>900800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>929500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E45" s="3">
         <v>52600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>41400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>121400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>342200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>344800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>336600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>260900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>99600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>134300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>99000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>58600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>62400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>48600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>35700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>151200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>55700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>70500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>110900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>34300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3608200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3751800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3321200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3291300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3287500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3158300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3170300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3211600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3610000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3806000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3816300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3791900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3987600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4485000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3607900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3900200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4026100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4643000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3838700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3543900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3427400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2849300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2848400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>21800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1700</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>5900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>25300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>54100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>53500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>55100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>4700</v>
       </c>
       <c r="AC47" s="3">
         <v>4700</v>
       </c>
       <c r="AD47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AE47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>4400</v>
       </c>
       <c r="AF47" s="3">
         <v>4400</v>
       </c>
       <c r="AG47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AH47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2131000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2176300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2177600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2215300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2253600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2300200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2302200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2343200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2411500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2470800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2494100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2530300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2527000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2574400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2191800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2226600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2320600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2249500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2212200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2235000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2167600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2123000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>823600</v>
+      </c>
+      <c r="E49" s="3">
         <v>827400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>831100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>835000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>838800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>841900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>824600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>828400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>832200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>836000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>839800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>833900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>790900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>780500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>107900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>108400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>109100</v>
-      </c>
-      <c r="T49" s="3">
-        <v>3600</v>
       </c>
       <c r="U49" s="3">
         <v>3600</v>
@@ -4259,25 +4370,25 @@
         <v>3600</v>
       </c>
       <c r="W49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="X49" s="3">
         <v>3700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>4300</v>
       </c>
       <c r="AB49" s="3">
         <v>4300</v>
       </c>
       <c r="AC49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AD49" s="3">
         <v>4400</v>
@@ -4286,13 +4397,16 @@
         <v>4400</v>
       </c>
       <c r="AF49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AG49" s="3">
         <v>4500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,103 +4598,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>192900</v>
+      </c>
+      <c r="E52" s="3">
         <v>193400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>186400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>186100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>183700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>363500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>409900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>603100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>632300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>623700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>588900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>585000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>556400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>536500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>692700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>803200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>554800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>624700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>574700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>606300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>611100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>653300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>624100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>601300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>502400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>497400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>504400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>476000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>494300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,103 +4794,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6764500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6950100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6538100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6545200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6574700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6666200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6713600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6989300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7490600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7737300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7740800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7741100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7867800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8383900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6604400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7043300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7001100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7606000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6701600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6345100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6297700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5685900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5682100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,578 +4966,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1138300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1106800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1030300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>974400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>948200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>919800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>848000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>810700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>762900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>720300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>644800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>607100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>540800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>558900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>483100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>512000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>740700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1058300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1140500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1116400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1072800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>902600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>882400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>837500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>819600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>693100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>762100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>726000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>691600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>579700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E58" s="3">
         <v>64800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>56000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>55100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>355400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>347700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>47800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>40200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>340700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>335500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>352800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>52700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>50200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>37600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>33300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>32400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>31400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>25000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>128100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>31100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>27900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>26700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1148400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1026700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1255500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1155400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1092200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>979000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1034100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1021500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1012900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1106200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1157900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>876400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>907000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>809800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>677700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>575900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>640700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>652200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>687600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>660400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>651100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>648100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>904800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>888500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>851100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>896800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>883200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>937800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2367700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2198300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2350000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2185800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2095500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1952500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2237500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2179900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1824900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1876000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1850500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1531400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1488000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1709400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1496300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1440700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1434100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1760700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1865700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1810100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1756300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1582100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1812200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3991200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4018700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3811000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3814900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3815800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3814900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3428000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3424800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3734000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3742700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3546700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3552700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3525200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3532900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2659000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3050600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2978200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2984100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2132200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2113300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2214900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1864000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1869700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1519400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1229000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1232800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1173400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1108000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1142600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1093700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1158700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1549500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1669800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1918800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2096700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2161600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2284600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1277100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1282500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1132400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1099300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1086700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>953000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1005400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1001700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>883800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>944600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>982800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>725400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>780900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>752400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>818800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>872200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,103 +5846,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7882200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7449800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7397500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7177600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7022900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6913700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6759700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6763900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7108900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7289000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7316500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7181300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7175300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7527400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5432900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5774300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5545200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5844600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5085100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4876900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4977100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4448300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4566200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,103 +6372,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E72" s="3">
         <v>616300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>540900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>745000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>951300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1232500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1475700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1604200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1727500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1781400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1902800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2017400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2153700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2326400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2623500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2780000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3036900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3201300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3146200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3027300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2871900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2713200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2548700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,103 +6764,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1117700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-499700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-859400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-632400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-448200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-247500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-46100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>225400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>381700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>448300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>424300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>559800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>692500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>856500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1171500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1269000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1455900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1761400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1616500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1468200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1320600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1237600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1115900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>954200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6960,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45379</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45197</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45106</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45015</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44833</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44378</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44287</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44105</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44014</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43923</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43734</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43643</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43552</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43370</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43279</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43188</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43006</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42915</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42824</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-616700</v>
+      </c>
+      <c r="E81" s="3">
         <v>75400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-204100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-206300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-281200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-243100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-127600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-122200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-52800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-120300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-113600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-135300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-171600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-295900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-155500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-255900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-162900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>67300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>131300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>167900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>163000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>177900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>168700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>145100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>125300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>122800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>147100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>141600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>108200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,103 +7199,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E83" s="3">
         <v>78700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>79200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>83900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>84200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>85200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>85700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>81600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>75100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>67100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>68100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>67300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>63000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>60500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>59300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>57000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>56800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>55100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>53700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>53000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>52500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>59500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7785,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-415600</v>
+      </c>
+      <c r="E89" s="3">
         <v>113700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-110500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-182800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-46200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-35700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-61500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-270200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-76500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>211000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-170200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-132100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-53100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-228400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-331300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>204100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>246900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>229500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>242200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>202500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>170200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>230600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>166600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>290600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>222300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>111700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>142500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7921,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-71500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-48500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-31000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-113400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-40900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-37100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-40800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8213,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-71300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-66700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-45800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-318600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-147300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-121200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-40900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-37100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-40700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-99700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8134,13 +8368,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>-1000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="K96" s="3">
         <v>-1100</v>
@@ -8149,16 +8383,16 @@
         <v>-1100</v>
       </c>
       <c r="M96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-1100</v>
       </c>
       <c r="O96" s="3">
         <v>-1100</v>
       </c>
       <c r="P96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="Q96" s="3">
         <v>-1000</v>
@@ -8167,52 +8401,55 @@
         <v>-1000</v>
       </c>
       <c r="S96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-12400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-12600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-12700</v>
       </c>
       <c r="W96" s="3">
         <v>-12700</v>
       </c>
       <c r="X96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="Y96" s="3">
         <v>-12600</v>
       </c>
       <c r="Z96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AE96" s="3">
         <v>-12000</v>
       </c>
       <c r="AF96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,289 +8739,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E100" s="3">
         <v>397500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>165200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>73500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-293700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>182300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-316400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>875100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-439100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>365500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>770900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-18100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-118100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>249700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-118100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>82900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>9500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>19400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-466100</v>
+      </c>
+      <c r="E102" s="3">
         <v>449400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-151500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-88300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-99700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-381700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-326800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>48000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>161300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-90000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-514000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>431000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-504800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>116500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-516800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>873200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>175900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>73100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>450900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>90200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>252600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>28600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>23600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>27300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,439 +656,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E7" s="2">
         <v>45379</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45197</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45106</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45015</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44833</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44378</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44287</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44105</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44014</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43923</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43734</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43643</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43552</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43370</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43279</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43188</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43006</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42915</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42824</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1491900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1702800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1812900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1438900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1364700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1431400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1320100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1276900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1257900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1174700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1070100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>980000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1002100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>876600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>806300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>644600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1077300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1959300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1919900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2016100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1967800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1835300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1813700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1725400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2138300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1521500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1492500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1395500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1432200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1369800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1193700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1277500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1130400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1056500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1033600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1012000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>956700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>904600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>914300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>905800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1087100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1757300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1647600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1723200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1658300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1534600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1543100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-233500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-435500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>291400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-53600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-30800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-49700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>83200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-19600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>44300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-53600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-9900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-55900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-28000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-108000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-261200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-9800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>202000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>272300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>292900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>309500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>300700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>270600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>289700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>225100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>290400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>261600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>273100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>236800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1123,106 +1136,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E12" s="3">
         <v>10600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1319,13 +1336,16 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1334,71 +1354,71 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>40200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>25600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>68500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-11000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1406,42 +1426,45 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>9100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>10800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>12100</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>10</v>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>10</v>
@@ -1458,11 +1481,11 @@
       <c r="O15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>10</v>
@@ -1479,8 +1502,8 @@
       <c r="V15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,204 +1574,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1823200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2230400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1597900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1572600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1485100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1526500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1458900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1272400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1362600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1216900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1149100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1136600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1099800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1030000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>982700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>983200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1011600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1244800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1863600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1713800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1776600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1734800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1591700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1591200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-331300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-527600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>215000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-133700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-120400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-95100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-138800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-104700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-42200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-79000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-156600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-97700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-129200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-106100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-176900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-367000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-167500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>95700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>206100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>239500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>233000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>243600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>222500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>217600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>159500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>226900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>202300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>204400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>160900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,498 +1813,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-20400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-117400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-44300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-42100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>34600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>37700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>94800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>31100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-49000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-9500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>11000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-253200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-447400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>273300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-52500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-132600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-99200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>80700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>14600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-38700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-119800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-305300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-149200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>166500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>260100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>297600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>282500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>296700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>287800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>262300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>220400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>284600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>267000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>267600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>221800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E22" s="3">
         <v>80200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>97600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>77500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>73600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>72400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>73300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>56800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>55100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>58900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>64900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>59100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>61500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>53000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>32200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>25800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-413200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-605500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>97000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-201500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-203900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-284900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-256400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-94400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-125200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-136000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-120600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-125700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-172900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-175300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-239900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-422000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-248700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>76000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>173000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>210900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>203200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>217700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>205700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>180500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>152300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>217900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>202900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>205600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>152500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-13200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-11000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>119800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-85200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-167600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-87200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>42900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>40100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>45500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>27500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>66400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>55900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>64000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>44300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,204 +2417,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-616500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>75600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-203900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-206900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-280600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-243200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-127300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-121700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-52400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-119400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-112700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-134700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-171200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-295100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-154700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-254400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-161500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>67500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>131300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>168000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>163100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>172200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>168800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>145200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>124800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>151500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>147000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>141600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>108200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-616700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>75400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-204100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-206300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-281200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-243100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-127600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-122200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-52800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-120300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-113600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-135300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-171600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-295900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-155500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-255900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-162900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>66900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>131300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>167900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>163000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>172500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>168700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>145100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>125300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>151500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>147100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>141600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>108200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2700,8 +2761,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>10</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>10</v>
@@ -2718,11 +2779,11 @@
       <c r="T29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V29" s="3">
         <v>400</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -2730,11 +2791,11 @@
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="3">
         <v>5400</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -2742,11 +2803,11 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,204 +3023,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>20400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>117400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>44300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>42100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-34600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-37700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-94800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-31100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>49000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>9500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>12300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-616700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>75400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-204100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-206300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-281200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-243100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-127600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-122200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-52800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-120300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-113600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-135300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-171600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-295900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-155500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-255900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-162900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>67300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>131300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>167900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>163000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>177900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>168700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>145100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>125300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>122800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>147100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>141600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>108200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,209 +3326,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-616700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>75400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-204100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-206300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-281200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-243100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-127600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-122200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-52800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-120300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-113600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-135300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-171600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-295900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-155500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-255900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-162900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>67300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>131300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>167900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>163000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>177900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>168700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>145100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>125300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>122800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>147100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>141600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>108200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E38" s="2">
         <v>45379</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45197</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45106</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45015</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44833</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44378</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44287</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44105</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44014</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43923</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43734</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43643</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43552</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43370</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43279</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43188</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43006</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42915</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42824</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,106 +3609,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E41" s="3">
         <v>352000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>823500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>374100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>525700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>567800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>658600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>670500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>770200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1151800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1478600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1430600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1269300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1359300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1873300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1441300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1947100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1833600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2350500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1477300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1301400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1228400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>773600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>683400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>593000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>437900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>423300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>726600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>696900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>672200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>697700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3719,652 +3809,673 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1568500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1404300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1108400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1206300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1080300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1113700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>990500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1073800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1064000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1029000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>904800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>938600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>875000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>887700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>852800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>722400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>627600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>889500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1074700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1287600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1209400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1175800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1014500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1198300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>722200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>851700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>824300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>818600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>660500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1893300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1797500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1767300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1690000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1636300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1549100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1470700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1392400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1345800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1387800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1382600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1325700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1305400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1395800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1422300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1183300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1225900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1168700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1118800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1015200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>970700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>991600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1012600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>931000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>900800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>929500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E45" s="3">
         <v>54400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>52600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>49000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>41400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>121400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>342200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>344800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>336600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>260900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>99600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>134300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>99000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>58600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>62400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>48600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>35700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>151200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>30400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>70500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>110900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>34300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3725500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3608200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3751800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3321200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3291300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3287500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3158300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3170300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3211600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3610000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3806000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3816300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3791900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3987600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4485000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3607900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3900200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4026100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4643000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3838700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3543900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3427400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2849300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2848400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E47" s="3">
         <v>8800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1700</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>10700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>25300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>54100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>53500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>55100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>4700</v>
       </c>
       <c r="AD47" s="3">
         <v>4700</v>
       </c>
       <c r="AE47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AF47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>4400</v>
       </c>
       <c r="AG47" s="3">
         <v>4400</v>
       </c>
       <c r="AH47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AI47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2096900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2131000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2176300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2177600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2215300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2253600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2300200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2302200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2343200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2411500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2470800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2494100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2530300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2527000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2574400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2191800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2226600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2320600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2249500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2212200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2235000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2167600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2123000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>819800</v>
+      </c>
+      <c r="E49" s="3">
         <v>823600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>827400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>831100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>835000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>838800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>841900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>824600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>828400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>832200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>836000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>839800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>833900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>790900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>780500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>107900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>108400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>109100</v>
-      </c>
-      <c r="U49" s="3">
-        <v>3600</v>
       </c>
       <c r="V49" s="3">
         <v>3600</v>
@@ -4373,25 +4484,25 @@
         <v>3600</v>
       </c>
       <c r="X49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Y49" s="3">
         <v>3700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>4300</v>
       </c>
       <c r="AC49" s="3">
         <v>4300</v>
       </c>
       <c r="AD49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AE49" s="3">
         <v>4400</v>
@@ -4400,13 +4511,16 @@
         <v>4400</v>
       </c>
       <c r="AG49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AH49" s="3">
         <v>4500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,106 +4718,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E52" s="3">
         <v>192900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>193400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>186400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>186100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>183700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>363500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>409900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>603100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>632300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>623700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>588900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>585000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>556400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>536500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>692700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>803200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>554800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>624700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>600100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>574700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>606300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>611100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>653300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>624100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>601300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>502400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>497400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>504400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>476000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>494300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,106 +4920,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6858600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6764500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6950100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6538100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6545200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6574700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6666200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6713600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6989300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7490600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7737300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7740800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7741100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7867800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8383900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6604400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7043300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7001100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7606000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6701600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6345100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6297700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5685900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5682100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,596 +5097,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1113900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1138300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1106800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1030300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>974400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>948200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>919800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>848000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>810700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>762900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>720300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>644800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>607100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>540800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>558900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>483100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>512000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>740700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1058300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1140500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1116400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1072800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>902600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>882400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>837500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>819600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>693100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>762100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>726000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>691600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>579700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E58" s="3">
         <v>81000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>56000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>53700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>355400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>347700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>40200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>340700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>335500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>352800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>52700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>50200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>37600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>33300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>32400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>31400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>25000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>128100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>31200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>31100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>27900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>26800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>26700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1663300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1148400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1026700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1255500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1155400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1092200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>979000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1034100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1021500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1012900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1106200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1157900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>876400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>907000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>809800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>677700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>575900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>640700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>652200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>687600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>660400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>651100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>648100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>904800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>888500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>851100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>896800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>883200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>937800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2854600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2367700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2198300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2350000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2185800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2095500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1952500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2237500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2179900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1824900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1876000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1850500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1531400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1488000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1709400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1496300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1440700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1434100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1760700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1865700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1810100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1756300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1582100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1812200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3984000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3991200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4018700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3811000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3814900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3815800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3814900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3428000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3424800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3734000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3742700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3546700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3552700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3525200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3532900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2659000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3050600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2978200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2984100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2132200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2113300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2214900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1864000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1869700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1533500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1519400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1229000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1232800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1173400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1108000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1142600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1093700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1158700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1549500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1669800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1918800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2096700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2161600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2284600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1277100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1282500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1132400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1099300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1086700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>953000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1005400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1001700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>883800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>944600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>982800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>725400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>780900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>752400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>818800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>872200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,106 +6004,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8376200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7882200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7449800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7397500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7177600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7022900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6913700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6759700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6763900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7108900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7289000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7316500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7181300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7175300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7527400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5432900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5774300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5545200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5844600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5085100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4876900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4977100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4448300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4566200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,106 +6546,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-415700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>616300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>540900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>745000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>951300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1232500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1475700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1604200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1727500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1781400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1902800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2017400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2153700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2326400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2623500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2780000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3036900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3201300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3146200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3027300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2871900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2713200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2548700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,106 +6950,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1517600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1117700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-499700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-859400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-632400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-448200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-247500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-46100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>225400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>381700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>448300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>424300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>559800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>692500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>856500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1171500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1269000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1455900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1761400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1616500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1468200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1320600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1237600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1115900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>954200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,209 +7152,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45470</v>
+      </c>
+      <c r="E80" s="2">
         <v>45379</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45197</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45106</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45015</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44833</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44378</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44287</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44105</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44014</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43923</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43734</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43643</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43552</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43370</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43279</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43188</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43006</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42915</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42824</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-616700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>75400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-204100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-206300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-281200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-243100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-127600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-122200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-52800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-120300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-113600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-135300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-171600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-295900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-155500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-255900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-162900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>67300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>131300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>167900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>163000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>177900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>168700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>145100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>125300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>122800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>147100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>141600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>108200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,106 +7398,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E83" s="3">
         <v>77900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>78700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>83900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>84200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>83800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>85200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>85700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>81600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>68100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>64700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>63500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>63000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>60500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>59300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>57900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>57000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>56800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>55100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>53700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>53000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>52500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>59500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,106 +8002,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-565500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-415600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>113700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-110500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-182800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-46200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-61500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-270200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-76500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>211000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-170200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-132100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-53100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-228400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-331300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>204100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>246900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>229500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>242200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>202500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>170200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>230600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>166600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>290600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>222300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>111700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>142500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,106 +8142,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-37500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-60600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-48500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-31000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-113400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-37100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,106 +8443,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-71300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-66700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-45800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-318600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-147300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-121200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-40900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-37100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-99700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8583,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8371,13 +8605,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>-1000</v>
       </c>
       <c r="K96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="L96" s="3">
         <v>-1100</v>
@@ -8386,16 +8620,16 @@
         <v>-1100</v>
       </c>
       <c r="N96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-1100</v>
       </c>
       <c r="P96" s="3">
         <v>-1100</v>
       </c>
       <c r="Q96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="R96" s="3">
         <v>-1000</v>
@@ -8404,52 +8638,55 @@
         <v>-1000</v>
       </c>
       <c r="T96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-12400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-12600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-12700</v>
       </c>
       <c r="X96" s="3">
         <v>-12700</v>
       </c>
       <c r="Y96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="Z96" s="3">
         <v>-12600</v>
       </c>
       <c r="AA96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AF96" s="3">
         <v>-12000</v>
       </c>
       <c r="AG96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,298 +8985,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>450400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>397500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>165200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>73500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-293700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>182300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-316400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>875100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-439100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>365500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-32000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>770900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-18100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-118100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>249700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>82900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-145700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-466100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>449400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-151500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-42100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-88300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-99700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-381700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-326800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>48000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>161300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-90000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-514000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>431000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-504800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>116500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-516800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>873200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>175900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>73100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>450900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>90200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>252600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>28600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>23600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>27300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,452 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E7" s="2">
         <v>45470</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45379</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45197</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45106</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45015</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44833</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44378</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44287</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44105</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44014</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43923</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43734</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43643</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43552</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43370</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43279</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43188</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43006</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42915</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42824</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1470600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1491900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1702800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1812900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1438900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1364700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1431400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1320100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1276900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1257900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1174700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1070100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>980000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1002100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>876600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>806300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>644600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1077300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1959300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1919900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2016100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1967800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1835300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1813700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1716600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1725400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2138300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1521500</v>
       </c>
-      <c r="G9" s="3">
-        <v>1492500</v>
-      </c>
       <c r="H9" s="3">
-        <v>1395500</v>
+        <v>1491700</v>
       </c>
       <c r="I9" s="3">
+        <v>1390600</v>
+      </c>
+      <c r="J9" s="3">
         <v>1432200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1369800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1193700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1277500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1130400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1056500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1033600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1012000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>956700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>904600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>914300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>905800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1087100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1757300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1647600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1723200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1658300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1534600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1543100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-233500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-435500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>291400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K10" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="L10" s="3">
+        <v>83200</v>
+      </c>
+      <c r="M10" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="N10" s="3">
+        <v>44300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>13600</v>
+      </c>
+      <c r="P10" s="3">
         <v>-53600</v>
       </c>
-      <c r="H10" s="3">
-        <v>-30800</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-49700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>83200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-19600</v>
-      </c>
-      <c r="M10" s="3">
-        <v>44300</v>
-      </c>
-      <c r="N10" s="3">
-        <v>13600</v>
-      </c>
-      <c r="O10" s="3">
-        <v>-53600</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-55900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-28000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-108000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-261200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-9800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>202000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>272300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>292900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>309500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>300700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>270600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>289700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>225100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>290400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>261600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>273100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>236800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1137,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E12" s="3">
         <v>13400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>18500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1339,89 +1356,92 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>23200</v>
+      </c>
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>900</v>
-      </c>
       <c r="I14" s="3">
-        <v>6300</v>
+        <v>5800</v>
       </c>
       <c r="J14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>9700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>40200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>25600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>68500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1429,45 +1449,48 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>9100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>10800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>12100</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>73400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>73700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>74200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>72600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>10</v>
+        <v>74400</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>10</v>
@@ -1484,11 +1507,11 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3">
         <v>2300</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>10</v>
@@ -1505,8 +1528,8 @@
       <c r="W15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1541,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1823200</v>
+        <v>1816800</v>
       </c>
       <c r="E17" s="3">
+        <v>1818800</v>
+      </c>
+      <c r="F17" s="3">
         <v>2230400</v>
       </c>
-      <c r="F17" s="3">
-        <v>1597900</v>
-      </c>
       <c r="G17" s="3">
-        <v>1572600</v>
+        <v>1586800</v>
       </c>
       <c r="H17" s="3">
-        <v>1485100</v>
+        <v>1570100</v>
       </c>
       <c r="I17" s="3">
-        <v>1526500</v>
+        <v>1477300</v>
       </c>
       <c r="J17" s="3">
+        <v>1556100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1458900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1272400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1362600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1216900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1149100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1136600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1099800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1030000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>982700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>983200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1011600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1244800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1863600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1713800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1776600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1734800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1591700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1591200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-331300</v>
+        <v>-346200</v>
       </c>
       <c r="E18" s="3">
+        <v>-326900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-527600</v>
       </c>
-      <c r="F18" s="3">
-        <v>215000</v>
-      </c>
       <c r="G18" s="3">
-        <v>-133700</v>
+        <v>226100</v>
       </c>
       <c r="H18" s="3">
-        <v>-120400</v>
+        <v>-131200</v>
       </c>
       <c r="I18" s="3">
-        <v>-95100</v>
+        <v>-112600</v>
       </c>
       <c r="J18" s="3">
+        <v>-124700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-138800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-104700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-42200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-79000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-156600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-97700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-129200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-106100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-176900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-367000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-167500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>95700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>206100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>239500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>233000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>243600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>222500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>217600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>159500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>226900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>202300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>204400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>160900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,513 +1847,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>40100</v>
       </c>
       <c r="E20" s="3">
-        <v>2300</v>
+        <v>15300</v>
       </c>
       <c r="F20" s="3">
-        <v>-20400</v>
+        <v>10100</v>
       </c>
       <c r="G20" s="3">
-        <v>9700</v>
+        <v>37100</v>
       </c>
       <c r="H20" s="3">
-        <v>-9900</v>
+        <v>-2500</v>
       </c>
       <c r="I20" s="3">
-        <v>-117400</v>
+        <v>16700</v>
       </c>
       <c r="J20" s="3">
+        <v>27100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-44300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-42100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>34600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>94800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>31100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>16100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-49000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-9500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>10500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>10700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-253200</v>
+        <v>-312900</v>
       </c>
       <c r="E21" s="3">
-        <v>-447400</v>
+        <v>-268500</v>
       </c>
       <c r="F21" s="3">
-        <v>273300</v>
+        <v>-463400</v>
       </c>
       <c r="G21" s="3">
-        <v>-44800</v>
+        <v>263300</v>
       </c>
       <c r="H21" s="3">
-        <v>-52500</v>
+        <v>-54500</v>
       </c>
       <c r="I21" s="3">
-        <v>-132600</v>
+        <v>-56700</v>
       </c>
       <c r="J21" s="3">
+        <v>-77400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-99200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-32800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-38700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-119800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-305300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-149200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>166500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>260100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>297600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>282500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>296700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>287800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>262300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>220400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>284600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>267000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>267600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>221800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>82300</v>
+        <v>83100</v>
       </c>
       <c r="E22" s="3">
-        <v>80200</v>
+        <v>76100</v>
       </c>
       <c r="F22" s="3">
-        <v>97600</v>
+        <v>73800</v>
       </c>
       <c r="G22" s="3">
-        <v>77500</v>
+        <v>71600</v>
       </c>
       <c r="H22" s="3">
-        <v>73600</v>
+        <v>72200</v>
       </c>
       <c r="I22" s="3">
-        <v>72400</v>
+        <v>69900</v>
       </c>
       <c r="J22" s="3">
+        <v>66600</v>
+      </c>
+      <c r="K22" s="3">
         <v>73300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>56800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>55100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>58900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>64900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>58800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>61500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>53000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>32200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-413200</v>
+        <v>-473800</v>
       </c>
       <c r="E23" s="3">
-        <v>-605500</v>
+        <v>-413000</v>
       </c>
       <c r="F23" s="3">
-        <v>97000</v>
+        <v>-605600</v>
       </c>
       <c r="G23" s="3">
+        <v>96900</v>
+      </c>
+      <c r="H23" s="3">
         <v>-201500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-203900</v>
-      </c>
       <c r="I23" s="3">
-        <v>-284900</v>
+        <v>-203400</v>
       </c>
       <c r="J23" s="3">
+        <v>-285600</v>
+      </c>
+      <c r="K23" s="3">
         <v>-256400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-125200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-63400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-136000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-120600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-125700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-172900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-175300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-239900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-422000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-248700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>76000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>173000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>210900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>203200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>217700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>205700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>180500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>152300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>217900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>202900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>205600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>152500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>119800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-85200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-167600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-87200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>41700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>45500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>35300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>27500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>66400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>55900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>64000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>44300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-415300</v>
+        <v>-476600</v>
       </c>
       <c r="E26" s="3">
-        <v>-616500</v>
+        <v>-415100</v>
       </c>
       <c r="F26" s="3">
-        <v>75600</v>
+        <v>-616600</v>
       </c>
       <c r="G26" s="3">
+        <v>75500</v>
+      </c>
+      <c r="H26" s="3">
         <v>-203900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-206900</v>
-      </c>
       <c r="I26" s="3">
-        <v>-280600</v>
+        <v>-206400</v>
       </c>
       <c r="J26" s="3">
+        <v>-281300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-243200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-127300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-121700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-119400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-112700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-134700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-171200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-295100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-154700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-254400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-161500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>67500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>131300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>168000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>163100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>172200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>168800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>145200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>124800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>151500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>147000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>141600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>108200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-476900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-415300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-616700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>75400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-204100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-206300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-281200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-243100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-127600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-122200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-120300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-113600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-171600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-295900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-155500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-255900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-162900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>66900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>131300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>167900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>163000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>172500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>168700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>145100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>125300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>151500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>147100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>141600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>108200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2764,8 +2825,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>10</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>10</v>
@@ -2782,11 +2843,11 @@
       <c r="U29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W29" s="3">
         <v>400</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
@@ -2794,11 +2855,11 @@
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA29" s="3">
         <v>5400</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
@@ -2806,11 +2867,11 @@
       <c r="AC29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -2824,8 +2885,11 @@
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-40100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2300</v>
+        <v>-15300</v>
       </c>
       <c r="F32" s="3">
-        <v>20400</v>
+        <v>-10100</v>
       </c>
       <c r="G32" s="3">
-        <v>-9700</v>
+        <v>-37100</v>
       </c>
       <c r="H32" s="3">
-        <v>9900</v>
+        <v>2500</v>
       </c>
       <c r="I32" s="3">
-        <v>117400</v>
+        <v>-16700</v>
       </c>
       <c r="J32" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="K32" s="3">
         <v>44300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>42100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-34600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-94800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-16100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>49000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>9500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-476900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-415300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-616700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>75400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-204100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-206300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-281200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-243100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-127600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-122200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-120300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-113600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-171600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-295900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-155500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-255900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-162900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>67300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>131300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>167900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>163000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>177900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>168700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>145100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>125300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>122800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>147100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>141600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>108200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-476900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-415300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-616700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>75400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-204100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-206300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-281200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-243100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-127600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-122200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-120300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-113600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-171600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-295900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-155500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-255900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-162900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>67300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>131300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>167900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>163000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>177900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>168700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>145100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>125300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>122800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>147100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>141600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>108200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E38" s="2">
         <v>45470</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45379</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45197</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45106</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45015</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44833</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44378</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44287</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44105</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44014</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43923</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43734</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43643</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43552</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43370</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43279</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43188</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43006</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42915</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42824</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,109 +3696,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>217600</v>
+      </c>
+      <c r="E41" s="3">
         <v>206000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>352000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>823500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>374100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>525700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>567800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>658600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>670500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>770200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1151800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1478600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1430600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1269300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1359300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1873300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1441300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1947100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1833600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2350500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1477300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1301400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1228400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>773600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>683400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>593000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>437900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>423300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>726600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>696900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>672200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>697700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,673 +3902,694 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1632100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1568500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1404300</v>
       </c>
-      <c r="F43" s="3">
-        <v>1108400</v>
-      </c>
       <c r="G43" s="3">
-        <v>1206300</v>
+        <v>1113700</v>
       </c>
       <c r="H43" s="3">
+        <v>1209000</v>
+      </c>
+      <c r="I43" s="3">
         <v>1080300</v>
       </c>
-      <c r="I43" s="3">
-        <v>1113700</v>
-      </c>
       <c r="J43" s="3">
+        <v>1117600</v>
+      </c>
+      <c r="K43" s="3">
         <v>990500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1073800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1064000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1029000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>904800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>938600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>875000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>887700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>852800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>722400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>627600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>889500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1074700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1287600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1209400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1175800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1014500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1198300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>722200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>851700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>824300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>818600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>660500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2020700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1893300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1797500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1767300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1690000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1636300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1549100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1470700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1392400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1345800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1387800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1382600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1325700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1305400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1395800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1422300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1183300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1225900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1168700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1118800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1015200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>970700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>991600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1012600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>931000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>900800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>929500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>57700</v>
+        <v>12100</v>
       </c>
       <c r="E45" s="3">
-        <v>54400</v>
+        <v>9900</v>
       </c>
       <c r="F45" s="3">
-        <v>52600</v>
+        <v>7700</v>
       </c>
       <c r="G45" s="3">
-        <v>50800</v>
+        <v>12400</v>
       </c>
       <c r="H45" s="3">
-        <v>49000</v>
+        <v>8300</v>
       </c>
       <c r="I45" s="3">
-        <v>56900</v>
+        <v>7400</v>
       </c>
       <c r="J45" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K45" s="3">
         <v>38500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>41400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>121400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>342200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>344800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>336600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>260900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>99600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>99000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>58600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>62400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>31600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>48600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>151200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>30400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>55700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>70500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>110900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>34300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>36900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3933800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3725500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3608200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3751800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3321200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3291300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3287500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3158300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3170300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3211600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3610000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3806000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3816300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3791900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3987600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4485000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3607900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3900200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4026100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4643000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3838700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3543900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3427400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2849300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2848400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>16800</v>
+        <v>1000</v>
       </c>
       <c r="E47" s="3">
-        <v>8800</v>
+        <v>800</v>
       </c>
       <c r="F47" s="3">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="G47" s="3">
-        <v>21800</v>
+        <v>800</v>
       </c>
       <c r="H47" s="3">
-        <v>17500</v>
+        <v>900</v>
       </c>
       <c r="I47" s="3">
-        <v>11100</v>
+        <v>900</v>
       </c>
       <c r="J47" s="3">
+        <v>400</v>
+      </c>
+      <c r="K47" s="3">
         <v>2300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1700</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>5900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>10400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>10700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>25300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>54100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>53500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>55100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>4700</v>
       </c>
       <c r="AE47" s="3">
         <v>4700</v>
       </c>
       <c r="AF47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AG47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>4400</v>
       </c>
       <c r="AH47" s="3">
         <v>4400</v>
       </c>
       <c r="AI47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2073100</v>
+      </c>
+      <c r="E48" s="3">
         <v>2096900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2131000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2176300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2177600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2215300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2253600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2300200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2302200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2343200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2411500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2470800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2494100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2530300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2527000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2574400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2191800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2226600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2300700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2320600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2249500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2212200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2235000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2167600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2123000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>819800</v>
+        <v>817400</v>
       </c>
       <c r="E49" s="3">
-        <v>823600</v>
+        <v>821600</v>
       </c>
       <c r="F49" s="3">
-        <v>827400</v>
+        <v>826000</v>
       </c>
       <c r="G49" s="3">
-        <v>831100</v>
+        <v>830900</v>
       </c>
       <c r="H49" s="3">
-        <v>835000</v>
+        <v>835200</v>
       </c>
       <c r="I49" s="3">
-        <v>838800</v>
+        <v>839900</v>
       </c>
       <c r="J49" s="3">
+        <v>844500</v>
+      </c>
+      <c r="K49" s="3">
         <v>841900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>824600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>828400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>832200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>836000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>839800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>833900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>790900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>780500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>107900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>108400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>109100</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3600</v>
       </c>
       <c r="W49" s="3">
         <v>3600</v>
@@ -4487,25 +4598,25 @@
         <v>3600</v>
       </c>
       <c r="Y49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>4300</v>
       </c>
       <c r="AD49" s="3">
         <v>4300</v>
       </c>
       <c r="AE49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AF49" s="3">
         <v>4400</v>
@@ -4514,13 +4625,16 @@
         <v>4400</v>
       </c>
       <c r="AH49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AI49" s="3">
         <v>4500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,109 +4838,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>199600</v>
+        <v>200900</v>
       </c>
       <c r="E52" s="3">
-        <v>192900</v>
+        <v>197700</v>
       </c>
       <c r="F52" s="3">
-        <v>193400</v>
+        <v>190400</v>
       </c>
       <c r="G52" s="3">
-        <v>186400</v>
+        <v>190200</v>
       </c>
       <c r="H52" s="3">
-        <v>186100</v>
+        <v>182100</v>
       </c>
       <c r="I52" s="3">
-        <v>183700</v>
+        <v>180800</v>
       </c>
       <c r="J52" s="3">
+        <v>173600</v>
+      </c>
+      <c r="K52" s="3">
         <v>363500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>409900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>603100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>632300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>623700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>588900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>585000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>556400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>536500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>692700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>803200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>554800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>624700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>600100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>574700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>606300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>611100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>653300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>624100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>601300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>502400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>497400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>504400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>476000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>494300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,109 +5046,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7049200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6858600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6764500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6950100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6538100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6545200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6574700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6666200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6713600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6989300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7490600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7737300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7740800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7741100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7867800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8383900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6604400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7043300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7001100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7606000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6701600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6345100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6297700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5685900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5682100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,614 +5228,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1091100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1113900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1138300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1106800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1030300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>974400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>948200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>919800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>848000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>810700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>762900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>720300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>644800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>607100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>540800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>558900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>483100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>512000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>740700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1058300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1140500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1116400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1072800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>902600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>882400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>837500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>819600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>693100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>762100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>726000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>691600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>579700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>77400</v>
+        <v>878000</v>
       </c>
       <c r="E58" s="3">
-        <v>81000</v>
+        <v>87000</v>
       </c>
       <c r="F58" s="3">
-        <v>64800</v>
+        <v>90400</v>
       </c>
       <c r="G58" s="3">
-        <v>64200</v>
+        <v>73900</v>
       </c>
       <c r="H58" s="3">
-        <v>56000</v>
+        <v>72600</v>
       </c>
       <c r="I58" s="3">
-        <v>55100</v>
+        <v>64300</v>
       </c>
       <c r="J58" s="3">
+        <v>63300</v>
+      </c>
+      <c r="K58" s="3">
         <v>53700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>355400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>347700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>49500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>40200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>340700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>335500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>352800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>52700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>50200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>37600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>33300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>31400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>25000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>128100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>31200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>31100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>27900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>26600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>26800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>26700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1663300</v>
+        <v>888500</v>
       </c>
       <c r="E59" s="3">
-        <v>1148400</v>
+        <v>1182800</v>
       </c>
       <c r="F59" s="3">
-        <v>1026700</v>
+        <v>632700</v>
       </c>
       <c r="G59" s="3">
-        <v>1255500</v>
+        <v>630300</v>
       </c>
       <c r="H59" s="3">
-        <v>1155400</v>
+        <v>749500</v>
       </c>
       <c r="I59" s="3">
-        <v>1092200</v>
+        <v>725200</v>
       </c>
       <c r="J59" s="3">
+        <v>556800</v>
+      </c>
+      <c r="K59" s="3">
         <v>979000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1034100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1021500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1012900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1106200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1157900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>876400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>907000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>809800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>677700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>575900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>640700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>652200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>687600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>660400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>651100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>648100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>904800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>888500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>851100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>896800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>883200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>937800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3432300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2854600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2367700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2198300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2350000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2185800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2095500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1952500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2237500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2179900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1824900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1876000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1850500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1531400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1488000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1709400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1496300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1440700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1434100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1760700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1865700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1810100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1756300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1582100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1812200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3984000</v>
+        <v>4263900</v>
       </c>
       <c r="E61" s="3">
-        <v>3991200</v>
+        <v>4064400</v>
       </c>
       <c r="F61" s="3">
-        <v>4018700</v>
+        <v>4074700</v>
       </c>
       <c r="G61" s="3">
-        <v>3811000</v>
+        <v>4103000</v>
       </c>
       <c r="H61" s="3">
+        <v>3895900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3897900</v>
+      </c>
+      <c r="J61" s="3">
+        <v>3900000</v>
+      </c>
+      <c r="K61" s="3">
         <v>3814900</v>
       </c>
-      <c r="I61" s="3">
-        <v>3815800</v>
-      </c>
-      <c r="J61" s="3">
-        <v>3814900</v>
-      </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3428000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3424800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3734000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3742700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3546700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3552700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3525200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3532900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2659000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3050600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2978200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2984100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2132200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2113300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2214900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1864000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1869700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1533500</v>
+        <v>982400</v>
       </c>
       <c r="E62" s="3">
-        <v>1519400</v>
+        <v>1142600</v>
       </c>
       <c r="F62" s="3">
-        <v>1229000</v>
+        <v>1143100</v>
       </c>
       <c r="G62" s="3">
-        <v>1232800</v>
+        <v>841500</v>
       </c>
       <c r="H62" s="3">
-        <v>1173400</v>
+        <v>809300</v>
       </c>
       <c r="I62" s="3">
-        <v>1108000</v>
+        <v>774300</v>
       </c>
       <c r="J62" s="3">
+        <v>695100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1142600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1093700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1158700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1549500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1669800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1918800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2096700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2161600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2284600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1277100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1282500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1132400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1099300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1086700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>953000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1005400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1001700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>883800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>944600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>982800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>725400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>780900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>752400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>818800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>872200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,109 +6162,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8376200</v>
+        <v>8985700</v>
       </c>
       <c r="E66" s="3">
-        <v>7882200</v>
+        <v>8372100</v>
       </c>
       <c r="F66" s="3">
-        <v>7449800</v>
+        <v>7878300</v>
       </c>
       <c r="G66" s="3">
-        <v>7397500</v>
+        <v>7446000</v>
       </c>
       <c r="H66" s="3">
-        <v>7177600</v>
+        <v>7393800</v>
       </c>
       <c r="I66" s="3">
-        <v>7022900</v>
+        <v>7174100</v>
       </c>
       <c r="J66" s="3">
+        <v>7019300</v>
+      </c>
+      <c r="K66" s="3">
         <v>6913700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6759700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6763900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7108900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7289000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7316500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7181300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7175300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7527400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5432900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5774300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5545200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5844600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5085100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4876900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4977100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4448300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4566200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,109 +6720,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-892600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-415700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>616300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>540900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>745000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>951300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1232500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1475700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1604200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1727500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1781400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1902800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2017400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2153700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2326400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2623500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2780000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3036900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3201300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3146200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3027300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2871900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2713200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2548700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,109 +7136,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1940900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1517600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1117700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-499700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-859400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-632400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-448200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-247500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-46100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>225400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>381700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>448300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>424300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>559800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>692500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>856500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1171500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1269000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1455900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1761400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1616500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1468200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1320600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1237600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1115900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>954200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45561</v>
+      </c>
+      <c r="E80" s="2">
         <v>45470</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45379</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45197</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45106</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45015</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44833</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44378</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44287</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44105</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44014</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43923</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43734</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43643</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43552</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43370</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43279</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43188</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43006</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42915</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42824</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-476900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-415300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-616700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>75400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-204100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-206300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-281200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-243100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-127600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-122200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-120300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-113600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-171600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-295900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-155500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-255900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-162900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>67300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>131300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>167900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>163000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>177900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>168700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>145100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>125300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>122800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>147100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>141600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>108200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,109 +7597,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>77700</v>
+        <v>73600</v>
       </c>
       <c r="E83" s="3">
-        <v>77900</v>
+        <v>72000</v>
       </c>
       <c r="F83" s="3">
-        <v>78700</v>
+        <v>73800</v>
       </c>
       <c r="G83" s="3">
+        <v>77000</v>
+      </c>
+      <c r="H83" s="3">
         <v>79200</v>
       </c>
-      <c r="H83" s="3">
-        <v>77800</v>
-      </c>
       <c r="I83" s="3">
-        <v>79900</v>
+        <v>77300</v>
       </c>
       <c r="J83" s="3">
+        <v>80200</v>
+      </c>
+      <c r="K83" s="3">
         <v>83900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>84200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>83800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>85200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>85700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>81600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>75100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>67100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>68100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>67300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>64700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>63500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>60500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>59300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>57900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>57000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>56800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>55100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>53700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>53000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>52500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>59500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,109 +8219,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-276400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-565500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-415600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>113700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-110500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-182800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-46200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-61500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-270200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-76500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>211000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-170200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-132100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-53100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-228400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-331300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>204100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>246900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>229500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>242200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>202500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>170200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>230600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>166600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>290600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>222300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>111700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>142500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,109 +8363,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-31600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-25200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-22900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-60600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-27600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-48500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-31000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-113400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-40900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,109 +8673,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-71300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-66700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-318600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-147300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-121200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-40900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-99700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,37 +8817,38 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-1000</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>-1000</v>
       </c>
       <c r="L96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="M96" s="3">
         <v>-1100</v>
@@ -8623,16 +8857,16 @@
         <v>-1100</v>
       </c>
       <c r="O96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-1100</v>
       </c>
       <c r="Q96" s="3">
         <v>-1100</v>
       </c>
       <c r="R96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="S96" s="3">
         <v>-1000</v>
@@ -8641,52 +8875,55 @@
         <v>-1000</v>
       </c>
       <c r="U96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-12400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-12600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-12700</v>
       </c>
       <c r="Y96" s="3">
         <v>-12700</v>
       </c>
       <c r="Z96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="AA96" s="3">
         <v>-12600</v>
       </c>
       <c r="AB96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AG96" s="3">
         <v>-12000</v>
       </c>
       <c r="AH96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,307 +9231,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>335900</v>
+      </c>
+      <c r="E100" s="3">
         <v>450400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>397500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>165200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-20100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-12700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-293700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>182300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-316400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>875100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-439100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>365500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-32000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>770900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-118100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>249700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>82900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1000</v>
+        <v>-4800</v>
       </c>
       <c r="E101" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F101" s="3">
+        <v>900</v>
+      </c>
+      <c r="G101" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K101" s="3">
+        <v>8600</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="T101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="W101" s="3">
+        <v>19400</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H101" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>900</v>
-      </c>
-      <c r="J101" s="3">
-        <v>8600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="AA101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>6600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>4400</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>19400</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>700</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-800</v>
-      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-145700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-466100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>449400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-151500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-42100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-88300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-99700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-381700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-326800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>48000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>161300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-514000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>431000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-504800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>116500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-516800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>873200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>175900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>73100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>450900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>90200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>252600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>27300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,465 +656,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45561</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45470</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45379</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45197</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45106</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45015</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44833</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44378</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44287</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44105</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44014</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43923</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43734</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43552</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43370</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43279</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43188</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43006</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42915</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42824</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1651300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1470600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1491900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1702800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1812900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1438900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1364700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1431400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1320100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1276900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1257900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1174700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1070100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>980000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1002100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>900800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>876600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>806300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>644600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1077300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1959300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1919900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2016100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1967800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1835300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1813700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2108700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1716600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1725400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2138300</v>
       </c>
-      <c r="G9" s="3">
-        <v>1521500</v>
-      </c>
       <c r="H9" s="3">
+        <v>1527200</v>
+      </c>
+      <c r="I9" s="3">
         <v>1491700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1390600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1432200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1369800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1193700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1277500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1130400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1056500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1033600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1012000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>956700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>904600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>914300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>905800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1087100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1757300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1647600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1723200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1658300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1534600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1543100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-457400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-246000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-233500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-435500</v>
       </c>
-      <c r="G10" s="3">
-        <v>291400</v>
-      </c>
       <c r="H10" s="3">
+        <v>285700</v>
+      </c>
+      <c r="I10" s="3">
         <v>-52800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-25900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-49700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-19600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>44300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-9900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-55900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-28000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-108000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-261200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-9800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>202000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>272300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>292900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>309500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>300700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>270600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>289700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>225100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>290400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>261600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>273100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>236800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,112 +1163,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E12" s="3">
         <v>10400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>18500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,92 +1375,95 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3600</v>
       </c>
-      <c r="G14" s="3">
-        <v>23200</v>
-      </c>
       <c r="H14" s="3">
+        <v>-55400</v>
+      </c>
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>69000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>9700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>40200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>25600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>68500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>3100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1452,48 +1471,51 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>9100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>10800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E15" s="3">
         <v>73400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>73700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>74300</v>
       </c>
       <c r="G15" s="3">
         <v>74300</v>
       </c>
       <c r="H15" s="3">
+        <v>74300</v>
+      </c>
+      <c r="I15" s="3">
         <v>74200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>72600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>74400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>10</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>10</v>
@@ -1510,11 +1532,11 @@
       <c r="Q15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="3">
         <v>2300</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>10</v>
@@ -1531,8 +1553,8 @@
       <c r="X15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1567,8 +1589,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1627,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2158600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1816800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1818800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2230400</v>
       </c>
-      <c r="G17" s="3">
-        <v>1586800</v>
-      </c>
       <c r="H17" s="3">
+        <v>1665400</v>
+      </c>
+      <c r="I17" s="3">
         <v>1570100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1477300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1556100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1458900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1272400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1362600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1216900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1149100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1136600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1099800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1030000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>982700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>983200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1011600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1244800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1863600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1713800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1776600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1734800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1591700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1591200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-507300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-346200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-326900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-527600</v>
       </c>
-      <c r="G18" s="3">
-        <v>226100</v>
-      </c>
       <c r="H18" s="3">
+        <v>147500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-131200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-112600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-124700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-138800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-104700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-42200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-79000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-156600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-97700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-129200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-106100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-176900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-367000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-167500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>95700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>206100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>239500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>233000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>243600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>222500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>217600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>159500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>226900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>202300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>204400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>160900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1848,528 +1880,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E20" s="3">
         <v>40100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10100</v>
       </c>
-      <c r="G20" s="3">
-        <v>37100</v>
-      </c>
       <c r="H20" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-44300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-42100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>34600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>94800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>31100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>16100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-49000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>10500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-395400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-312900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-268500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-463400</v>
       </c>
-      <c r="G21" s="3">
-        <v>263300</v>
-      </c>
       <c r="H21" s="3">
+        <v>178800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-54500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-56700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-77400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-99200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>80700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-32800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-38700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-119800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-305300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-149200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>166500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>260100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>297600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>282500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>296700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>287800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>262300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>220400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>284600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>267000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>267600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>221800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E22" s="3">
         <v>83100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>76100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>73800</v>
       </c>
-      <c r="G22" s="3">
-        <v>71600</v>
-      </c>
       <c r="H22" s="3">
+        <v>65700</v>
+      </c>
+      <c r="I22" s="3">
         <v>72200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>69900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>66600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>73300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>55100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>58900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>64900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>58800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>59100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>59800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>61500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>53000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>32200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>25800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>18800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-649000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-473800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-413000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-605600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-201500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-203400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-285600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-256400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-94400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-125200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-63400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-136000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-120600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-125700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-172900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-175300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-239900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-422000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-248700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>76000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>173000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>210900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>203200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>217700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>205700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>180500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>152300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>217900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>202900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>205600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>152500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-13200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>119800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-85200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-167600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-87200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>42900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>40100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>45500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>36900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>35300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>27500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>66400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>55900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>64000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>44300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2520,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-630700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-476600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-415100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-616600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>75500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-203900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-206400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-281300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-243200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-127300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-121700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-52400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-119400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-112700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-134700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-171200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-295100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-154700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-254400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-161500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>67500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>131300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>168000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>163100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>172200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>168800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>145200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>124800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>151500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>147000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>141600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>108200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-630900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-476900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-415300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-616700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>75400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-204100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-206300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-281200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-243100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-127600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-122200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-52800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-120300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-135300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-171600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-295900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-155500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-255900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-162900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>66900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>131300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>167900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>163000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>172500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>168700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>145100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>125300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>151500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>147100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>141600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>108200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2841,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2828,8 +2888,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>10</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>10</v>
@@ -2846,11 +2906,11 @@
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X29" s="3">
         <v>400</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
@@ -2858,11 +2918,11 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>5400</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -2870,11 +2930,11 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>10</v>
@@ -2888,8 +2948,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3055,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3162,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-37100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="I32" s="3">
         <v>2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>44300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>42100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-34600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-94800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-31100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-16100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>49000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>9500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-630900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-476900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-415300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-616700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>75400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-204100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-206300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-281200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-243100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-127600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-122200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-52800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-120300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-135300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-171600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-295900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-155500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-255900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-162900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>67300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>131300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>167900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>163000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>177900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>168700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>145100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>125300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>122800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>147100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>141600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>108200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3483,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-630900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-476900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-415300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-616700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>75400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-204100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-206300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-281200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-243100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-127600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-122200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-52800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-120300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-135300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-171600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-295900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-155500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-255900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-162900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>67300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>131300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>167900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>163000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>177900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>168700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>145100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>125300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>122800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>147100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>141600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>108200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45561</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45470</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45379</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45197</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45106</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45015</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44833</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44378</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44287</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44105</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44014</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43923</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43734</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43552</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43370</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43279</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43188</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43006</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42915</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42824</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3743,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,112 +3782,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>537000</v>
+      </c>
+      <c r="E41" s="3">
         <v>217600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>206000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>352000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>823500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>374100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>525700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>567800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>658600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>670500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>770200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1151800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1478600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1430600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1269300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1359300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1873300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1441300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1947100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1833600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2350500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1477300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1301400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1228400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>773600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>683400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>593000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>437900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>423300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>726600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>696900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>672200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>697700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3905,694 +3994,715 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1179800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1632100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1568500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1404300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1113700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1209000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1080300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1117600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>990500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1073800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1064000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1029000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>904800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>938600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>875000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>887700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>852800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>722400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>627600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>889500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1074700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1287600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1209400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1175800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1014500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1198300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>722200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>851700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>824300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>818600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>660500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1891700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2020700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1893300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1797500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1767300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1690000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1636300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1549100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1470700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1392400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1345800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1387800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1382600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1325700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1305400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1395800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1422300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1183300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1225900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1168700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1118800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1015200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>970700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>991600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1012600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>931000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>900800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>929500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>110600</v>
+      </c>
+      <c r="E45" s="3">
         <v>12100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>41400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>121400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>342200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>344800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>336600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>260900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>99600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>134300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>99000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>58600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>62400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>31600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>48600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>35700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>151200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>30400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>55700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>70500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>110900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>34300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>36900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3760500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3933800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3725500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3608200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3751800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3321200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3291300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3287500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3158300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3170300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3211600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3610000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3806000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3816300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3791900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3987600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4485000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3607900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3900200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4026100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4643000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3838700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3543900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3427400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2849300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2848400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>900</v>
       </c>
       <c r="I47" s="3">
         <v>900</v>
       </c>
       <c r="J47" s="3">
+        <v>900</v>
+      </c>
+      <c r="K47" s="3">
         <v>400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1700</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>5900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>14100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>10700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>25300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>54100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>55100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>4700</v>
       </c>
       <c r="AF47" s="3">
         <v>4700</v>
       </c>
       <c r="AG47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AH47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>4400</v>
       </c>
       <c r="AI47" s="3">
         <v>4400</v>
       </c>
       <c r="AJ47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AK47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2026900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2073100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2096900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2131000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2176300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2177600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2215300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2253600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2300200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2302200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2343200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2411500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2470800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2494100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2530300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2527000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2574400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2191800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2226600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2300700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2320600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2249500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2212200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2235000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2167600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2123000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>780200</v>
+      </c>
+      <c r="E49" s="3">
         <v>817400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>821600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>826000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>830900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>835200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>839900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>844500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>841900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>824600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>828400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>832200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>836000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>839800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>833900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>790900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>780500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>107900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>108400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>109100</v>
-      </c>
-      <c r="W49" s="3">
-        <v>3600</v>
       </c>
       <c r="X49" s="3">
         <v>3600</v>
@@ -4601,25 +4711,25 @@
         <v>3600</v>
       </c>
       <c r="Z49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>4300</v>
       </c>
       <c r="AE49" s="3">
         <v>4300</v>
       </c>
       <c r="AF49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AG49" s="3">
         <v>4400</v>
@@ -4628,13 +4738,16 @@
         <v>4400</v>
       </c>
       <c r="AI49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4850,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,112 +4957,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>194200</v>
+      </c>
+      <c r="E52" s="3">
         <v>200900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>197700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>190400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>190200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>182100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>180800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>173600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>363500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>409900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>603100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>632300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>623700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>588900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>585000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>556400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>536500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>692700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>803200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>554800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>624700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>600100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>574700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>606300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>611100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>653300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>624100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>601300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>502400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>497400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>504400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>476000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>494300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,112 +5171,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6762800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7049200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6858600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6764500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6950100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6538100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6545200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6574700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6666200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6713600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6989300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7490600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7737300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7740800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7741100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7867800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8383900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6604400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7043300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7001100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7606000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6701600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6345100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6297700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5685900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5682100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5319,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,632 +5358,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1041100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1091100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1113900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1138300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1106800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1030300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>974400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>948200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>919800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>848000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>810700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>762900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>720300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>644800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>607100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>540800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>558900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>483100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>512000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>740700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1058300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1140500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1116400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1072800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>902600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>882400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>837500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>819600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>693100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>762100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>726000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>691600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>579700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>966500</v>
+      </c>
+      <c r="E58" s="3">
         <v>878000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>87000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>90400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>73900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>72600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>64300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>63300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>355400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>347700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>49100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>49500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>40200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>340700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>335500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>352800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>52700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>50200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>37600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>33300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>25000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>128100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>31200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>31100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>27900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>26600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>26800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>26700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1095600</v>
+      </c>
+      <c r="E59" s="3">
         <v>888500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1182800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>632700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>630300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>749500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>725200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>556800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>979000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1034100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1021500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1012900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1106200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1157900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>876400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>907000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>809800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>677700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>575900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>640700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>652200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>687600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>660400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>651100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>648100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>904800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>888500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>851100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>896800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>883200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>937800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3567400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3432300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2854600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2367700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2198300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2350000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2185800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2095500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1952500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2237500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2179900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1824900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1876000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1850500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1531400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1488000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1709400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1496300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1440700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1434100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1760700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1865700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1810100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1756300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1582100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1812200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4411500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4263900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4064400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4074700</v>
       </c>
-      <c r="G61" s="3">
-        <v>4103000</v>
-      </c>
       <c r="H61" s="3">
+        <v>4283000</v>
+      </c>
+      <c r="I61" s="3">
         <v>3895900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3897900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3900000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3814900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3428000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3424800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3734000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3742700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3546700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3552700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3525200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3532900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2659000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3050600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2978200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2984100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2132200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2113300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2214900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1864000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1869700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E62" s="3">
         <v>982400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1142600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1143100</v>
       </c>
-      <c r="G62" s="3">
-        <v>841500</v>
-      </c>
       <c r="H62" s="3">
+        <v>661500</v>
+      </c>
+      <c r="I62" s="3">
         <v>809300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>774300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>695100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1142600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1093700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1158700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1549500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1669800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1918800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2096700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2161600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2284600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1277100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1282500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1132400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1099300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1086700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>953000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1005400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1001700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>883800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>944600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>982800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>725400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>780900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>752400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>818800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>872200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6105,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6212,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,112 +6319,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9378800</v>
+      </c>
+      <c r="E66" s="3">
         <v>8985700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8372100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7878300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7446000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7393800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7174100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7019300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6913700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6759700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6763900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7108900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7289000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7316500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7181300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7175300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7527400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5432900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5774300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5545200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5844600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5085100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4876900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4977100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4448300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4566200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6467,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6572,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6679,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6786,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,112 +6893,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1523500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-892600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-415700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>616300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>540900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>745000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>951300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1232500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1475700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1604200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1727500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1781400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1902800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2017400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2153700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2326400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2623500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2780000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3036900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3201300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3146200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3027300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2871900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2713200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2548700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7107,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7214,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,112 +7321,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2621500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1940900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1517600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1117700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-499700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-859400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-632400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-448200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-247500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-46100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>225400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>381700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>448300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>424300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>559800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>692500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>856500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1171500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1269000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1455900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1761400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1616500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1468200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1320600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1237600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1115900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>954200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7535,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45561</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45470</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45379</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45197</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45106</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45015</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44833</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44378</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44287</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44105</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44014</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43923</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43734</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43552</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43370</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43279</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43188</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43006</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42915</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42824</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-630900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-476900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-415300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-616700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>75400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-204100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-206300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-281200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-243100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-127600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-122200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-52800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-120300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-113600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-135300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-171600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-295900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-155500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-255900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-162900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>67300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>131300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>167900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>163000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>177900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>168700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>145100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>125300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>122800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>147100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>141600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>108200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,112 +7795,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E83" s="3">
         <v>73600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>72000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>73800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>80200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>83900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>84200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>83800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>85200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>85700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>81600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>80300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>75100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>68100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>67300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>63000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>60500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>59300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>57900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>57000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>56800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>55100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>53700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>53000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>52500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>59500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8007,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8114,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8221,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8328,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,112 +8435,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-276400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-565500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-415600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>113700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-110500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-182800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-46200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-61500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-270200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-76500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>211000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-27500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-170200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-132100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-53100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-228400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-331300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>204100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>246900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>229500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>242200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>202500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>170200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>230600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>166600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>290600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>222300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>111700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>142500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,112 +8583,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-71500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-27600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-48500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-113400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8795,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,112 +8902,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-71300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-66700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-45800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-26400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-318600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-147300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-121200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-40900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-99700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9050,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8844,14 +9077,14 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>-1000</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>-1000</v>
       </c>
       <c r="M96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="N96" s="3">
         <v>-1100</v>
@@ -8860,16 +9093,16 @@
         <v>-1100</v>
       </c>
       <c r="P96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-1100</v>
       </c>
       <c r="R96" s="3">
         <v>-1100</v>
       </c>
       <c r="S96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="T96" s="3">
         <v>-1000</v>
@@ -8878,52 +9111,55 @@
         <v>-1000</v>
       </c>
       <c r="V96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-12400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-12600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-12700</v>
       </c>
       <c r="Z96" s="3">
         <v>-12700</v>
       </c>
       <c r="AA96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="AB96" s="3">
         <v>-12600</v>
       </c>
       <c r="AC96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AH96" s="3">
         <v>-12000</v>
       </c>
       <c r="AI96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9262,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9369,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,316 +9476,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>229700</v>
+      </c>
+      <c r="E100" s="3">
         <v>335900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>450400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>397500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>165200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>73500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-293700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>182300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-316400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>875100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-439100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>365500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>770900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-118100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>249700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>82900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>8600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-6800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>19400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>319700</v>
+      </c>
+      <c r="E102" s="3">
         <v>12700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-145700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-466100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>449400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-151500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-42100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-99700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-381700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-326800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>48000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>161300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-90000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-514000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>431000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-504800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>116500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-516800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>873200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>175900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>73100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>450900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>90200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>252600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>27300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,477 +656,490 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45750</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45470</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45379</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45197</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45106</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45015</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44833</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44378</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44287</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44105</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44014</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43923</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43734</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43643</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43552</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43370</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43279</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43188</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43006</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42915</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1521800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1651300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1470600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1491900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1702800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1812900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1438900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1364700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1431400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1320100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1276900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1257900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1174700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1070100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>980000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1002100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>900800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>876600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>806300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>644600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1077300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1959300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1919900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2016100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1967800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1835300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1813700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1982900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2108700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1716600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1725400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2138300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1527200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1491700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1390600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1432200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1369800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1193700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1277500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1130400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1056500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1033600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1012000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>956700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>904600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>914300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>905800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1087100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1757300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1647600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1723200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1658300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1534600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1543100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-461100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-457400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-246000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-233500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-435500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>285700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-52800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-25900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-49700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>83200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-19600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-53600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-9900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-55900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-28000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-108000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-261200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-9800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>202000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>272300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>292900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>309500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>300700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>270600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>289700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>225100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>290400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>261600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>273100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>236800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1164,115 +1177,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E12" s="3">
         <v>13100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>8200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>18500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>11100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>10000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1378,95 +1395,98 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="E14" s="3">
         <v>89000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4900</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3">
         <v>-55400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>69000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>9700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>40200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>25600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>68500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>12100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1474,51 +1494,54 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>9100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>12100</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E15" s="3">
         <v>70900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>73400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>73700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>74300</v>
       </c>
       <c r="H15" s="3">
         <v>74300</v>
       </c>
       <c r="I15" s="3">
+        <v>74300</v>
+      </c>
+      <c r="J15" s="3">
         <v>74200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>72600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>74400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>10</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>10</v>
@@ -1535,11 +1558,11 @@
       <c r="R15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T15" s="3">
         <v>2300</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>10</v>
@@ -1556,8 +1579,8 @@
       <c r="Y15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1592,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,222 +1654,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2065700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2158600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1816800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1818800</v>
       </c>
-      <c r="G17" s="3">
-        <v>2230400</v>
-      </c>
       <c r="H17" s="3">
+        <v>2226800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1665400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1570100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1477300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1556100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1458900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1272400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1362600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1216900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1149100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1136600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1099800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1030000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>982700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>983200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1011600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1244800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1863600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1713800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1776600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1734800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1591700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1591200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-543900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-507300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-346200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-326900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-527600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-524000</v>
+      </c>
+      <c r="I18" s="3">
         <v>147500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-131200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-112600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-124700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-138800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-104700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-42200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-79000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-156600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-97700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-129200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-106100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-176900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-367000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-167500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>95700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>206100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>239500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>233000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>243600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>222500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>217600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>159500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>226900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>202300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>204400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>160900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,543 +1914,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-41000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>40100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>10100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>43000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>16700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-44300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-42100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>34600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>94800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>31100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>16100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-49000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>11000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-504200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-395400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-312900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-268500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-463400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-459800</v>
+      </c>
+      <c r="I21" s="3">
         <v>178800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-54500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-56700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-77400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-99200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>13700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>14600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-32800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-38700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-119800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-305300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-149200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>166500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>260100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>297600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>282500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>296700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>287800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>262300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>220400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>284600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>267000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>267600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>221800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E22" s="3">
         <v>88900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>83100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>73800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>65700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>72200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>69900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>66600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>73300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>56800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>55100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>58900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>64900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>58800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>59100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>59800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>61500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>53000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>48600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>32200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>25800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-606700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-649000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-473800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-413000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-605600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>96900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-201500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-203400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-285600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-256400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-94400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-125200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-63400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-136000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-120600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-125700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-172900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-175300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-239900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-422000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-248700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>76000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>173000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>210900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>203200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>217700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>205700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>180500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>152300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>217900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>202900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>205600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>152500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-18300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-13200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>119800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-85200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-167600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-87200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>40100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>45500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>36900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>27500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>66400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>55900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>44300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,222 +2572,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-612700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-630700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-476600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-415100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-616600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>75500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-203900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-206400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-281300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-243200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-127300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-121700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-52400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-119400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-112700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-134700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-171200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-295100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-154700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-254400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-161500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>67500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>131300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>168000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>163100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>172200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>168800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>145200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>124800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>151500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>147000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>108200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-612900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-630900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-476900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-415300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-616700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>75400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-204100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-206300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-281200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-243100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-127600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-122200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-52800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-113600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-135300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-171600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-295900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-155500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-255900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-162900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>66900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>131300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>167900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>163000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>172500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>168700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>145100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>125300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>151500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>147100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>108200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2902,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2891,8 +2952,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>10</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>10</v>
@@ -2909,11 +2970,11 @@
       <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y29" s="3">
         <v>400</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -2921,11 +2982,11 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>5400</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -2933,11 +2994,11 @@
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>10</v>
@@ -2951,8 +3012,11 @@
       <c r="AK29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,222 +3232,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E32" s="3">
         <v>41000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-40100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-10100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-43000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-16700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>44300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>42100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-34600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-94800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-31100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-16100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>49000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>9500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>11000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>12300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-612900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-630900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-476900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-415300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-616700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>75400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-204100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-206300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-281200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-243100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-127600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-122200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-52800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-113600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-135300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-171600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-295900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-155500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-255900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-162900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>67300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>131300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>167900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>163000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>177900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>168700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>145100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>125300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>122800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>147100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>108200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,227 +3562,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-612900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-630900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-476900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-415300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-616700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>75400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-204100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-206300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-281200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-243100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-127600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-122200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-52800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-113600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-135300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-171600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-295900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-155500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-255900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-162900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>67300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>131300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>167900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>163000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>177900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>168700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>145100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>125300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>122800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>147100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>108200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45750</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45470</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45379</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45197</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45106</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45015</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44833</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44378</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44287</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44105</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44014</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43923</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43734</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43643</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43552</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43370</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43279</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43188</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43006</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42915</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,115 +3869,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E41" s="3">
         <v>537000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>217600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>206000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>352000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>823500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>374100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>525700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>567800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>658600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>670500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>770200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1151800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1478600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1430600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1269300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1359300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1873300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1441300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1947100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1833600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2350500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1477300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1301400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1228400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>773600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>683400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>593000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>437900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>423300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>726600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>696900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>672200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>697700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3997,715 +4087,736 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1180600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1179800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1632100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1568500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1404300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1113700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1209000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1080300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1117600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>990500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1073800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1064000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1029000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>904800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>938600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>875000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>887700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>852800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>722400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>627600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>889500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1074700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1287600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1209400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1175800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1014500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1198300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>722200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>851700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>824300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>818600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>660500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2019800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1891700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2020700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1893300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1797500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1767300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1690000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1636300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1549100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1470700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1392400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1345800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1387800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1382600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1325700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1305400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1395800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1422300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1183300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1225900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1168700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1118800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1015200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>970700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>991600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1012600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>931000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>900800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>929500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E45" s="3">
         <v>110600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>41400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>121400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>342200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>344800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>336600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>260900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>99600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>134300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>99000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>58600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>62400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>31600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>151200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>30400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>55700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>70500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>110900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>34300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>36900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3504300</v>
+      </c>
+      <c r="E46" s="3">
         <v>3760500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3933800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3725500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3608200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3751800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3321200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3291300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3287500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3158300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3170300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3211600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3610000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3806000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3816300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3791900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3987600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4485000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3607900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3900200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4026100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4643000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3838700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3543900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3427400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2849300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2848400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
         <v>900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>900</v>
       </c>
       <c r="J47" s="3">
         <v>900</v>
       </c>
       <c r="K47" s="3">
+        <v>900</v>
+      </c>
+      <c r="L47" s="3">
         <v>400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1700</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>5900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>10400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>14100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>9700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>10700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>25300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>54100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>53500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>55100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AF47" s="3">
-        <v>4700</v>
       </c>
       <c r="AG47" s="3">
         <v>4700</v>
       </c>
       <c r="AH47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AI47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>4400</v>
       </c>
       <c r="AJ47" s="3">
         <v>4400</v>
       </c>
       <c r="AK47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AL47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2013500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2026900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2073100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2096900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2131000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2176300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2177600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2215300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2253600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2300200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2302200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2343200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2411500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2470800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2494100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2530300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2527000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2574400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2191800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2226600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2300700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2320600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2249500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2212200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2235000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2167600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2123000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>776600</v>
+      </c>
+      <c r="E49" s="3">
         <v>780200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>817400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>821600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>826000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>830900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>835200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>839900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>844500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>841900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>824600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>828400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>832200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>836000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>839800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>833900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>790900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>780500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>107900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>108400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>109100</v>
-      </c>
-      <c r="X49" s="3">
-        <v>3600</v>
       </c>
       <c r="Y49" s="3">
         <v>3600</v>
@@ -4714,25 +4825,25 @@
         <v>3600</v>
       </c>
       <c r="AA49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AE49" s="3">
-        <v>4300</v>
       </c>
       <c r="AF49" s="3">
         <v>4300</v>
       </c>
       <c r="AG49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AH49" s="3">
         <v>4400</v>
@@ -4741,13 +4852,16 @@
         <v>4400</v>
       </c>
       <c r="AJ49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AK49" s="3">
         <v>4500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,115 +5077,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>175100</v>
+      </c>
+      <c r="E52" s="3">
         <v>194200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>197700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>190400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>190200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>182100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>180800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>173600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>363500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>409900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>603100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>632300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>623700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>588900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>585000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>556400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>536500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>692700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>803200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>554800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>624700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>600100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>574700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>606300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>611100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>653300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>624100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>601300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>502400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>497400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>504400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>476000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>494300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,115 +5297,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6477500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6762800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7049200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6858600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6764500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6950100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6538100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6545200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6574700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6666200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6713600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6989300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7490600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7737300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7740800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7741100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7867800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8383900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6604400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7043300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7001100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7606000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6701600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6345100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6297700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5685900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5682100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,650 +5489,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1083100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1041100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1091100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1113900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1138300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1106800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1030300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>974400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>948200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>919800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>848000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>810700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>762900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>720300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>644800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>607100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>540800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>558900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>483100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>512000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>740700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1058300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1140500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1116400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1072800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>902600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>882400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>837500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>819600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>693100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>762100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>726000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>691600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>579700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>522700</v>
+      </c>
+      <c r="E58" s="3">
         <v>966500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>878000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>87000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>90400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>73900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>64300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>63300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>53700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>355400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>347700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>49100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>49500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>47900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>40200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>340700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>335500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>352800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>52700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>50200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>37600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>33300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>31400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>25000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>128100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>31200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>31100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>27900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>26600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>26700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1256100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1095600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>888500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1182800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>632700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>630300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>749500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>725200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>556800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>979000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1034100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1021500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1012900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1106200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1157900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>876400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>907000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>809800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>677700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>575900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>640700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>652200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>687600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>660400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>651100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>648100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>904800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>888500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>851100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>896800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>883200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>937800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3392600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3567400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3432300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2854600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2367700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2198300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2350000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2185800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2095500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1952500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2237500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2179900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1824900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1876000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1850500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1531400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1488000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1709400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1496300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1440700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1434100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1760700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1865700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1810100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1756300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1582100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1812200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4867900</v>
+      </c>
+      <c r="E61" s="3">
         <v>4411500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4263900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4064400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4074700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4283000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3895900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3897900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3900000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3814900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3428000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3424800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3734000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3742700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3546700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3552700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3525200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3532900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2659000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3050600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2978200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2984100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2132200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2113300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2214900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1864000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1869700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1163400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1118000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>982400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1142600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1143100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>661500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>809300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>774300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>695100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1142600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1093700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1158700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1549500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1669800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1918800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2096700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2161600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2284600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1277100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1282500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1132400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1099300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1086700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>953000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1005400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1001700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>883800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>944600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>982800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>725400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>780900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>752400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>818800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>872200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,115 +6477,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9670900</v>
+      </c>
+      <c r="E66" s="3">
         <v>9378800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8985700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8372100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7878300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7446000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7393800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7174100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7019300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6913700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6759700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6763900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7108900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7289000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7316500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7181300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7175300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7527400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5432900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5774300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5545200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5844600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5085100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4876900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4977100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4448300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4566200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,115 +7067,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2136400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1523500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-892600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-415700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>616300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>540900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>745000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>951300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1232500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1475700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1604200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1727500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1781400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1902800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2017400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2153700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2326400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2623500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2780000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3036900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3201300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3146200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3027300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2871900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2713200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2548700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,115 +7507,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3199100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2621500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1940900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1517600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1117700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-499700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-859400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-632400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-448200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-247500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-46100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>225400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>381700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>448300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>424300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>559800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>692500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>856500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1171500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1269000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1455900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1761400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1616500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1468200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1320600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1237600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1115900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>954200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,227 +7727,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45750</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45470</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45379</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45197</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45106</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45015</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44833</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44378</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44287</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44105</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44014</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43923</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43734</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43643</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43552</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43370</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43279</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43188</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43006</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42915</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42824</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-612900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-630900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-476900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-415300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-616700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>75400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-204100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-206300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-281200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-243100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-127600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-122200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-52800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-113600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-135300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-171600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-295900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-155500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-255900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-162900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>67300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>131300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>167900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>163000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>177900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>168700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>145100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>125300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>122800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>147100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>141600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>108200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,8 +7994,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7805,106 +8004,109 @@
         <v>73500</v>
       </c>
       <c r="E83" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F83" s="3">
         <v>73600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>72000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>73800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>77300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>80200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>83900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>84200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>83800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>85200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>85700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>81600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>80000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>80300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>75100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>67100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>68100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>67300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>64700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>63500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>63000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>60500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>59300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>57900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>57000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>56800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>55100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>53700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>53000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>52500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>59500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,115 +8652,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-419500</v>
+      </c>
+      <c r="E89" s="3">
         <v>136600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-276400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-565500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-415600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>113700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-110500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-182800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-35700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-61500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-270200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-76500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>211000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-27500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-170200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-132100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-53100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-228400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-331300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>204100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>246900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>229500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>242200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>202500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>170200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>230600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>166600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>290600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>222300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>111700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>142500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,115 +8804,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-45700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-31600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-71500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-27600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-48500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-31000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-113400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,115 +9132,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-71300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-28400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-66700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-41400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-34200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-318600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-147300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-121200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-99700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,8 +9284,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,14 +9314,14 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>-1000</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>-1000</v>
       </c>
       <c r="N96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="O96" s="3">
         <v>-1100</v>
@@ -9096,16 +9330,16 @@
         <v>-1100</v>
       </c>
       <c r="Q96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-1100</v>
       </c>
       <c r="S96" s="3">
         <v>-1100</v>
       </c>
       <c r="T96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="U96" s="3">
         <v>-1000</v>
@@ -9114,52 +9348,55 @@
         <v>-1000</v>
       </c>
       <c r="W96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-12400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-12700</v>
       </c>
       <c r="AA96" s="3">
         <v>-12700</v>
       </c>
       <c r="AB96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="AC96" s="3">
         <v>-12600</v>
       </c>
       <c r="AD96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AI96" s="3">
         <v>-12000</v>
       </c>
       <c r="AJ96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,325 +9722,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E100" s="3">
         <v>229700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>335900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>450400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>397500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>165200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>73500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-293700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>182300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-316400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>875100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-439100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>365500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-32000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>770900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>249700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>82900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>9500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>19400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-313200</v>
+      </c>
+      <c r="E102" s="3">
         <v>319700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-145700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-466100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>449400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-151500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-88300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-99700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-381700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-326800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>48000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>161300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-90000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-514000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>431000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-504800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>116500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-516800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>873200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>175900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>73100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>450900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>90200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>252600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>28600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>23600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>27300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-130100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SPR</t>
   </si>
@@ -656,490 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45841</v>
+      </c>
+      <c r="E7" s="2">
         <v>45750</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45470</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45379</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45197</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45106</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45015</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44833</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44378</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44287</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44105</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44014</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43923</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43734</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43643</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43552</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43370</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43279</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43188</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43006</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42824</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1635100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1521800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1651300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1470600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1491900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1702800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1812900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1438900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1364700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1431400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1320100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1276900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1257900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1174700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1070100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>980000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1002100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>876600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>806300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>644600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1077300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1959300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1919900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2016100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1967800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1835300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1813700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1836900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1736100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1714600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1748200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1826100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1694100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1711400</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1866500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1982900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2108700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1716600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1725400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2138300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1527200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1491700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1390600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1432200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1369800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1193700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1277500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1130400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1056500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1033600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1012000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>956700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>904600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>914300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>905800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1087100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1757300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1647600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1723200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1658300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1534600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1543100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1547200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1511000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1424200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1486600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1855200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1421000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1333200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1439400</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-231400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-461100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-457400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-246000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-233500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-435500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>285700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-52800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-25900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-49700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-19600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>44300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-53600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-9900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-55900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-28000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-108000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-261200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>202000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>272300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>292900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>309500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>300700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>270600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>289700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>225100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>290400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>261600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-29100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>273100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>236800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>272000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1178,118 +1191,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E12" s="3">
         <v>14500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>10600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>19000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>18500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>11100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>10000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>5000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1398,98 +1415,101 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-58800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>89000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-55400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>69000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>25600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>68500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>12100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1497,54 +1517,57 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>10800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>12100</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E15" s="3">
         <v>67700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>70900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>73400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>73700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>74300</v>
       </c>
       <c r="I15" s="3">
         <v>74300</v>
       </c>
       <c r="J15" s="3">
+        <v>74300</v>
+      </c>
+      <c r="K15" s="3">
         <v>74200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>72600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>74400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>10</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>10</v>
@@ -1561,11 +1584,11 @@
       <c r="S15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" s="3">
         <v>2300</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>10</v>
@@ -1582,8 +1605,8 @@
       <c r="Z15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1618,8 +1641,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1655,228 +1681,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1937400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2065700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2158600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1816800</v>
       </c>
-      <c r="G17" s="3">
-        <v>1818800</v>
-      </c>
       <c r="H17" s="3">
+        <v>1807500</v>
+      </c>
+      <c r="I17" s="3">
         <v>2226800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1665400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1570100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1477300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1556100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1458900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1272400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1362600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1216900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1149100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1136600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1099800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1030000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>982700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>983200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1011600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1244800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1863600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1713800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1776600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1734800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1591700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1591200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1619300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1576600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1487700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1545900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1918200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1489700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1409100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1497000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-302300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-543900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-507300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-346200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-326900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-315600</v>
+      </c>
+      <c r="I18" s="3">
         <v>-524000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>147500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-131200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-112600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-124700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-138800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-104700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-42200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-79000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-156600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-97700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-129200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-106100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-176900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-367000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-167500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>95700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>206100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>239500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>233000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>243600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>222500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>217600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>159500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>226900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>202300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-92100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>204400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>160900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1915,558 +1948,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E20" s="3">
         <v>28000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-41000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>40100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>10100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>43000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-44300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-42100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>34600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>37700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>94800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>31100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>16100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-10000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-49000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>11000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>10700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-275200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-504200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-395400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-312900</v>
       </c>
-      <c r="G21" s="3">
-        <v>-268500</v>
-      </c>
       <c r="H21" s="3">
+        <v>-257200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-459800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>178800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-54500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-56700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-77400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-99200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>14600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-32800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-38700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-119800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-305300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-149200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>166500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>260100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>297600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>282500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>296700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>287800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>262300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>220400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>284600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>267000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-28600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>267600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>221800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>264400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E22" s="3">
         <v>84900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>88900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>83100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>76100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>73800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>65700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>72200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>69900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>66600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>73300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>56800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>55100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>58900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>64900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>58800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>59100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>53000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>32200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>18800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-604500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-606700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-649000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-473800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-413000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-605600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>96900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-201500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-203400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-285600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-256400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-94400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-125200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-136000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-120600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-125700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-172900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-175300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-239900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-422000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-248700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>76000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>173000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>210900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>203200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>217700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>205700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>180500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>152300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>217900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>202900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-91800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>205600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>152500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>201900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E24" s="3">
         <v>6000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-18300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-13200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-16600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>119800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-85200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-167600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-87200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>41700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>45500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>36900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>35300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>27500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>66400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>55900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-35000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>64000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>44300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2575,228 +2624,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-630800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-612700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-630700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-476600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-415100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-616600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>75500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-203900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-206400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-281300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-243200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-127300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-121700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-119400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-112700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-134700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-171200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-295100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-154700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-254400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-161500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>67500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>131300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>168000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>163100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>172200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>168800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>145200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>124800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>151500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>147000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>141600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>108200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-631000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-612900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-630900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-476900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-415300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-616700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>75400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-204100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-206300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-281200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-243100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-127600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-122200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-120300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-113600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-135300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-171600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-295900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-155500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-255900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-162900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>66900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>131300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>167900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>163000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>172500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>168700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>145100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>125300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>151500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>147100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-56800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>141600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>108200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2905,8 +2963,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2955,8 +3016,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
@@ -2973,11 +3034,11 @@
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="3">
         <v>400</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -2985,11 +3046,11 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>5400</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -2997,11 +3058,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-28700</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -3015,8 +3076,11 @@
       <c r="AL29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3125,8 +3189,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3235,228 +3302,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>41000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-40100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-10100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-43000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>44300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>42100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-34600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-94800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-31100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-16100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>10000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>49000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>9500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>12300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-631000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-612900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-630900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-476900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-415300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-616700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>75400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-204100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-206300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-281200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-243100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-127600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-122200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-120300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-113600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-135300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-171600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-295900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-155500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-255900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-162900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>67300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>131300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>167900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>163000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>177900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>168700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>145100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>125300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>122800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>147100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-56800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>141600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>108200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3565,233 +3641,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-631000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-612900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-630900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-476900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-415300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-616700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>75400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-204100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-206300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-281200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-243100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-127600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-122200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-120300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-113600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-135300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-171600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-295900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-155500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-255900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-162900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>67300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>131300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>167900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>163000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>177900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>168700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>145100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>125300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>122800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>147100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-56800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>141600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>108200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45841</v>
+      </c>
+      <c r="E38" s="2">
         <v>45750</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45470</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45379</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45197</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45106</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45015</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44833</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44378</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44287</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44105</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44014</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43923</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43734</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43643</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43552</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43370</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43279</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43188</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43006</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42824</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3830,8 +3915,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3870,118 +3956,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>369600</v>
+      </c>
+      <c r="E41" s="3">
         <v>220200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>537000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>217600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>206000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>352000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>823500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>374100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>525700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>567800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>658600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>670500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>770200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1151800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1478600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1430600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1269300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1359300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1873300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1441300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1947100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1833600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2350500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1477300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1301400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1228400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>773600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>683400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>593000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>437900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>423300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>726600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>696900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>672200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>697700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>670400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4090,736 +4180,757 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>788300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1180600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1179800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1632100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1568500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1404300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1113700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1209000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1080300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1117600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>990500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1073800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1064000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1029000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>904800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>938600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>875000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>887700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>852800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>722400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>627600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>889500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1074700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1287600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1209400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1175800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1014500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1198300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1181000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1205900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>722200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>851700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>824300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>818600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>660500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>748600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1345100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2019800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1891700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2020700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1893300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1797500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1767300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1690000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1636300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1549100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1470700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1392400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1345800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1387800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1382600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1325700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1305400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1395800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1422300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1183300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1225900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1168700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1118800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1015200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>970700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>991600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1012600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>931000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>900800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>929500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1449900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1363200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1325700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1473000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1515300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1488100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1225900</v>
+      </c>
+      <c r="E45" s="3">
         <v>27900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>110600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>121400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>342200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>344800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>336600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>260900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>99600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>134300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>99000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>58600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>62400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>48600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>35700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>151200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>30400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>55700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>70500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>110900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>34300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>36900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>25100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3768600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3504300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3760500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3933800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3725500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3608200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3751800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3321200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3291300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3287500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3158300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3170300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3211600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3610000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3806000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3816300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3791900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3987600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4485000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3607900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3900200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4026100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4643000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3838700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3543900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3427400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2849300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2848400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2826000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2603700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2651100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3012000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2957800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2998100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2910400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2932200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>900</v>
       </c>
       <c r="K47" s="3">
         <v>900</v>
       </c>
       <c r="L47" s="3">
+        <v>900</v>
+      </c>
+      <c r="M47" s="3">
         <v>400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1700</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>5900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>10400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>14100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>9700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>10700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>25300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>54100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>53500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>55100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>55600</v>
-      </c>
-      <c r="AG47" s="3">
-        <v>4700</v>
       </c>
       <c r="AH47" s="3">
         <v>4700</v>
       </c>
       <c r="AI47" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>4500</v>
-      </c>
-      <c r="AJ47" s="3">
-        <v>4400</v>
       </c>
       <c r="AK47" s="3">
         <v>4400</v>
       </c>
       <c r="AL47" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AM47" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1567600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2013500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2026900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2073100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2096900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2131000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2176300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2177600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2215300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2253600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2300200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2302200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2343200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2411500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2470800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2494100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2530300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2527000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2574400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2191800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2226600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2300700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2320600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2249500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2212200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2235000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2167600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2123000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2102600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2105400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2105300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2018700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1991400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1991600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1934700</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>750400</v>
+      </c>
+      <c r="E49" s="3">
         <v>776600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>780200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>817400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>821600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>826000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>830900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>835200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>839900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>844500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>841900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>824600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>828400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>832200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>836000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>839800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>833900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>790900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>780500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>107900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>108400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>109100</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>3600</v>
       </c>
       <c r="Z49" s="3">
         <v>3600</v>
@@ -4828,25 +4939,25 @@
         <v>3600</v>
       </c>
       <c r="AB49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC49" s="3">
         <v>3700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4000</v>
-      </c>
-      <c r="AF49" s="3">
-        <v>4300</v>
       </c>
       <c r="AG49" s="3">
         <v>4300</v>
       </c>
       <c r="AH49" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="AI49" s="3">
         <v>4400</v>
@@ -4855,13 +4966,16 @@
         <v>4400</v>
       </c>
       <c r="AK49" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AL49" s="3">
         <v>4500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4970,8 +5084,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5080,118 +5197,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E52" s="3">
         <v>175100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>194200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>197700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>190400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>190200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>182100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>180800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>173600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>363500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>409900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>603100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>632300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>623700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>588900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>585000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>556400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>536500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>692700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>803200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>554800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>624700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>600100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>574700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>606300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>611100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>653300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>624100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>601300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>502400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>497400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>504400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>476000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>494300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>485000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5300,118 +5423,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6238100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6477500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6762800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7049200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6858600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6764500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6950100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6538100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6545200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6574700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6666200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6713600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6989300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7490600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7737300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7740800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7741100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7867800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8383900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6604400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7043300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7001100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7606000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6701600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6345100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6297700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5685900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5682100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5611800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5370300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5267800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5537200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5462500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5469200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5405200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5361200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5450,8 +5579,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5490,668 +5620,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>852400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1083100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1041100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1091100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1113900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1138300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1106800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1030300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>974400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>948200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>919800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>848000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>810700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>762900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>720300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>644800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>607100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>540800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>558900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>483100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>512000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>740700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1058300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1140500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1116400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1072800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>902600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>882400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>837500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>819600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>693100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>762100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>726000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>691600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>579700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>591800</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1212500</v>
+      </c>
+      <c r="E58" s="3">
         <v>522700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>966500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>878000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>87000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>90400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>72600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>64300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>63300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>53700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>355400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>347700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>49100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>49500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>47800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>47900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>40200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>340700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>335500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>352800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>52700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>50200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>37600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>33300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>32400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>31400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>25000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>128100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>31200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>31100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>27900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>26800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>26700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2374000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1256100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1095600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>888500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1182800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>632700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>630300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>749500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>725200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>556800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>979000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1034100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1021500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1012900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1106200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1157900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>876400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>907000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>809800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>677700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>575900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>640700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>652200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>687600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>660400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>651100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>648100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>904800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>888500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>851100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>896800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1146000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1085100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>883200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>937800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>902300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4879200</v>
+      </c>
+      <c r="E60" s="3">
         <v>3392600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3567400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3432300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2854600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2367700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2198300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2350000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2185800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2095500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1952500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2237500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2179900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1824900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1876000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1850500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1531400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1488000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1709400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1496300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1440700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1434100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1760700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1865700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1810100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1756300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1582100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1812200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1854100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1701900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1621000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1936000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1837700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1601600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1544200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1528300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4220600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4867900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4411500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4263900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4064400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4074700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4283000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3895900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3897900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3900000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3814900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3428000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3424800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3734000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3742700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3546700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3552700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3525200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3532900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2659000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3050600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2978200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2984100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2132200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2113300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2214900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1864000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1869700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1858400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1112600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1119900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1060900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1060600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1063900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1060000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1071100</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>692200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1163400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1118000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>982400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1142600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1143100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>661500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>809300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>774300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>695100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1142600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1093700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1158700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1549500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1669800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1918800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2096700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2161600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2284600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1277100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1282500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1132400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1099300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1086700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>953000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1005400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1001700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>883800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>944600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>982800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>725400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>780900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>752400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>818800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>872200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>952500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6260,8 +6409,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6522,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6480,118 +6635,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10027800</v>
+      </c>
+      <c r="E66" s="3">
         <v>9670900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9378800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8985700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8372100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7878300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7446000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7393800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7174100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7019300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6913700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6759700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6763900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7108900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7289000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7316500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7181300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7175300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7527400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5432900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5774300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5545200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5844600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5085100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4876900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4977100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4448300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4566200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4657600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3797800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3466800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3778300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3651200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3484800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3476900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3552400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6630,8 +6791,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6740,8 +6902,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6850,8 +7015,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6960,8 +7128,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7070,118 +7241,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2767400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2136400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1523500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-892600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-415700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>616300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>540900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>745000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>951300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1232500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1475700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1604200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1727500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1781400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1902800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2017400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2153700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2326400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2623500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2780000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3036900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3201300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3146200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3027300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2871900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2713200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2548700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2392500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2260000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2422400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2310900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2186800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2243700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2113900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2017700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7290,8 +7467,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7400,8 +7580,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7510,118 +7693,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3795600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-3199100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2621500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1940900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1517600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1117700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-499700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-859400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-632400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-448200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-247500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-46100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>225400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>381700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>448300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>424300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>559800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>692500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>856500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1171500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1269000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1455900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1761400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1616500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1468200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1320600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1237600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1115900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>954200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1572500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1801000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1758900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1811300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1984400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1928300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1808800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7730,233 +7919,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45841</v>
+      </c>
+      <c r="E80" s="2">
         <v>45750</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45470</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45379</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45197</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45106</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45015</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44833</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44378</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44287</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44105</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44014</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43923</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43734</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43643</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43552</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43370</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43279</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43188</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43006</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42915</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42824</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42642</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-631000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-612900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-630900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-476900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-415300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-616700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>75400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-204100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-206300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-281200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-243100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-127600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-122200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-120300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-113600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-135300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-171600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-295900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-155500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-255900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-162900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>67300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>131300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>167900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>163000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>177900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>168700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>145100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>125300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>122800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>147100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-56800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>141600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>108200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>144900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7995,118 +8193,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>73500</v>
+        <v>65500</v>
       </c>
       <c r="E83" s="3">
         <v>73500</v>
       </c>
       <c r="F83" s="3">
-        <v>73600</v>
+        <v>73500</v>
       </c>
       <c r="G83" s="3">
-        <v>72000</v>
+        <v>74200</v>
       </c>
       <c r="H83" s="3">
+        <v>64400</v>
+      </c>
+      <c r="I83" s="3">
         <v>73800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>77300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>83900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>84200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>83800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>85200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>85700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>81600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>80000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>80300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>75100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>67100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>68100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>67300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>64700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>63500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>63000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>60500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>59300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>57900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>57000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>56800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>55100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>53700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>53000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>52500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>59500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8215,8 +8417,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8325,8 +8530,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8435,8 +8643,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8545,8 +8756,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8655,118 +8869,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-419500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>136600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-276400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-565500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-415600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>113700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-110500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-182800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-35700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-61500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-270200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-76500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>211000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-27500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-170200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-132100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-53100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-228400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-331300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>204100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>246900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>229500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>242200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>202500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>170200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>230600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>166600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-50900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>290600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>222300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>111700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>142500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>265600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8805,118 +9025,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-45700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-60600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-36700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-48500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-113400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-40900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-100300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-61200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-134400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-47500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-81200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-97200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-52100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9025,8 +9249,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9135,118 +9362,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="E94" s="3">
         <v>107900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-46400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-71300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-66700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-57400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-318600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-17000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-147300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-121200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-40900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-99700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-61100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-134500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-50400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-47300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-40600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-97200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-51500</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9285,8 +9518,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9317,14 +9551,14 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>-1000</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>-1000</v>
       </c>
       <c r="O96" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="P96" s="3">
         <v>-1100</v>
@@ -9333,16 +9567,16 @@
         <v>-1100</v>
       </c>
       <c r="R96" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="S96" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-1100</v>
       </c>
       <c r="T96" s="3">
         <v>-1100</v>
       </c>
       <c r="U96" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="V96" s="3">
         <v>-1000</v>
@@ -9351,52 +9585,55 @@
         <v>-1000</v>
       </c>
       <c r="X96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-12400</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-12700</v>
       </c>
       <c r="AB96" s="3">
         <v>-12700</v>
       </c>
       <c r="AC96" s="3">
-        <v>-12600</v>
+        <v>-12700</v>
       </c>
       <c r="AD96" s="3">
         <v>-12600</v>
       </c>
       <c r="AE96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-11500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-11700</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-12000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-12000</v>
       </c>
       <c r="AK96" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9505,8 +9742,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9615,8 +9855,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9725,334 +9968,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>342700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>229700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>335900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>450400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>397500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>165200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-293700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>182300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-316400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>875100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-439100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>365500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>770900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>249700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-118100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>82900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-105900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-213600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-154300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-343400</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>8600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>19400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-313200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>319700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-145700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-466100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>449400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-151500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-42100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-88300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-99700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-381700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-326800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>48000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>161300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-90000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-514000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>431000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-504800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>116500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-516800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>873200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>175900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>73100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>450900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>90200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>252600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-306600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>28600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-20000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>27300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-130100</v>
       </c>
     </row>
